--- a/gc-ms results/260930 raw oil.xlsx
+++ b/gc-ms results/260930 raw oil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\Notes\gc-ms results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21F3B48C-B168-4237-BBA3-F307A82E25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{98511B39-85CC-4B67-8FBF-F2CEF1AB28CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9DDEE15F-E737-4B6C-AA01-47268D57280C}"/>
   </bookViews>
@@ -1481,6 +1481,23 @@
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{02696040-A310-4945-97A4-2FB32B401A3D}" name="Table1" displayName="Table1" ref="A1:H195" totalsRowShown="0">
+  <autoFilter ref="A1:H195" xr:uid="{02696040-A310-4945-97A4-2FB32B401A3D}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{01AC00D2-410B-4476-B377-1C3B8197E384}" name="Component RT"/>
+    <tableColumn id="2" xr3:uid="{1133B22A-391B-4B5C-91B2-6E57F5886970}" name="Compound Name"/>
+    <tableColumn id="3" xr3:uid="{E38942FF-10BF-4BBC-8FC3-13FC41C0966F}" name="Match Factor"/>
+    <tableColumn id="4" xr3:uid="{7F272C7A-D3F0-45C0-8BCB-62A2B442E9A3}" name="Best Hit"/>
+    <tableColumn id="5" xr3:uid="{2DC9BF57-9B26-4EE7-800B-2A5F5C551CA3}" name="Formula"/>
+    <tableColumn id="6" xr3:uid="{18902260-5B9A-48CF-A7D0-647D0203620B}" name="Area %"/>
+    <tableColumn id="7" xr3:uid="{4D7F21DC-EE76-40BF-B1F3-C4638D394C59}" name="Area % Max."/>
+    <tableColumn id="8" xr3:uid="{5109D0E5-1D89-49C1-83D5-3564056D1BCA}" name="Base Peak Area"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1801,7 +1818,13 @@
   <dimension ref="A1:I195"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="14.88671875" customWidth="1"/>
     <col min="2" max="2" width="51.77734375" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -5715,5 +5738,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/gc-ms results/260930 raw oil.xlsx
+++ b/gc-ms results/260930 raw oil.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\Notes\gc-ms results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{98511B39-85CC-4B67-8FBF-F2CEF1AB28CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BFC335-ADF9-4868-B7AF-509B182ACF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9DDEE15F-E737-4B6C-AA01-47268D57280C}"/>
   </bookViews>
   <sheets>
     <sheet name="260930 raw oil" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="311">
   <si>
     <t>Component RT</t>
   </si>
@@ -46,9 +59,6 @@
     <t>Base Peak Area</t>
   </si>
   <si>
-    <t>MZ</t>
-  </si>
-  <si>
     <t>Phenol</t>
   </si>
   <si>
@@ -938,6 +948,24 @@
   </si>
   <si>
     <t>C17H16O4</t>
+  </si>
+  <si>
+    <t>phenol</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>methoxy</t>
+  </si>
+  <si>
+    <t>ester</t>
+  </si>
+  <si>
+    <t>amide</t>
+  </si>
+  <si>
+    <t>carboxylic acid</t>
   </si>
 </sst>
 </file>
@@ -1483,7 +1511,21 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{02696040-A310-4945-97A4-2FB32B401A3D}" name="Table1" displayName="Table1" ref="A1:H195" totalsRowShown="0">
-  <autoFilter ref="A1:H195" xr:uid="{02696040-A310-4945-97A4-2FB32B401A3D}"/>
+  <autoFilter ref="A1:H195" xr:uid="{02696040-A310-4945-97A4-2FB32B401A3D}">
+    <filterColumn colId="2">
+      <customFilters>
+        <customFilter operator="greaterThan" val="85"/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="greaterThan" val="100000"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H195">
+    <sortCondition ref="A1:A195"/>
+  </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{01AC00D2-410B-4476-B377-1C3B8197E384}" name="Component RT"/>
     <tableColumn id="2" xr3:uid="{1133B22A-391B-4B5C-91B2-6E57F5886970}" name="Compound Name"/>
@@ -1815,19 +1857,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05663A3C-3C2C-4760-A06E-2E5E378BF6B9}">
-  <dimension ref="A1:I195"/>
+  <dimension ref="A1:N195"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" customWidth="1"/>
     <col min="2" max="2" width="51.77734375" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="15.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1853,1515 +1898,1574 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J1" t="s">
+        <v>305</v>
+      </c>
+      <c r="K1" t="s">
+        <v>307</v>
+      </c>
+      <c r="L1" t="s">
+        <v>308</v>
+      </c>
+      <c r="M1" t="s">
+        <v>309</v>
+      </c>
+      <c r="N1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3.1799054323826201</v>
+      </c>
+      <c r="B2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2">
+        <v>89.212334563582701</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H2">
+        <v>29375.767883561799</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>4.2110670063696096</v>
+      </c>
+      <c r="B3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3">
+        <v>77.079469975011193</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H3">
+        <v>3496.0919390127701</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4.23448639810759</v>
+      </c>
+      <c r="B4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4">
+        <v>88.139288707531605</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4">
+        <v>26789.263654456001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4.2393737685011903</v>
+      </c>
+      <c r="B5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5">
+        <v>75.989414880563402</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H5">
+        <v>19150.127014097299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4.6303679995145002</v>
+      </c>
+      <c r="B6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6">
+        <v>90.668534998273699</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H6">
+        <v>13068.351013822299</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5.37273448999093</v>
+      </c>
+      <c r="B7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7">
+        <v>90.416773671599202</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7">
+        <v>65357.922859203703</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>5.3766850903912999</v>
+      </c>
+      <c r="B8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8">
+        <v>87.963176399796595</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H8">
+        <v>54152.145098895198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>5.7559266958886504</v>
+      </c>
+      <c r="B9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9">
+        <v>88.989662979746498</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9">
+        <v>19988.389436862599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>6.0113559101513303</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10">
+        <v>97.561169402453302</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10">
+        <v>97958.357444017107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>6.0318943995866903</v>
+      </c>
+      <c r="B11" t="s">
+        <v>280</v>
+      </c>
+      <c r="C11">
+        <v>78.9136734098918</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>281</v>
+      </c>
+      <c r="H11">
+        <v>6620.7053621443301</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>6.7367122934712604</v>
+      </c>
+      <c r="B12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12">
+        <v>90.692259515772307</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12">
+        <v>57727.953314653198</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>6.7878696891479704</v>
+      </c>
+      <c r="B13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13">
+        <v>80.116289290942007</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>61737.255655543297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>6.8368060723470601</v>
+      </c>
+      <c r="B14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14">
+        <v>88.560790370128899</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>132</v>
+      </c>
+      <c r="H14">
+        <v>34740.820103188598</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>7.1541843982103597</v>
+      </c>
+      <c r="B15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15">
+        <v>85.193960490128703</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>218</v>
+      </c>
+      <c r="H15">
+        <v>14421.4445384545</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>7.3386309821888904</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16">
+        <v>70.365115244838407</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16">
+        <v>4457.1163890152002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>7.3566008039928104</v>
+      </c>
+      <c r="B17" t="s">
+        <v>289</v>
+      </c>
+      <c r="C17">
+        <v>87.880473533074706</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>177</v>
+      </c>
+      <c r="H17">
+        <v>4085.9812283676001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>7.4990067141985497</v>
+      </c>
+      <c r="B18" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18">
+        <v>75.545009979857596</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18">
+        <v>7103.02467172242</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>7.7565122990738704</v>
+      </c>
+      <c r="B19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19">
+        <v>70.558911824126497</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H19">
+        <v>23247.744464137599</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>7.7601624677887102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20">
+        <v>90.510368916000104</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20">
+        <v>34902.493095443097</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>7.8295239439419202</v>
+      </c>
+      <c r="B21" t="s">
+        <v>188</v>
+      </c>
+      <c r="C21">
+        <v>82.601815731963299</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>156</v>
+      </c>
+      <c r="H21">
+        <v>18126.656668075299</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>8.0179614989319692</v>
+      </c>
+      <c r="B22" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>8.0179614989319692</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C22">
+        <v>98.575237163466895</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>98.575237163466895</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2">
+      <c r="H22">
         <v>9757329.7736495901</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>11.4526922770967</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="I22">
+        <f>J22+H59+H159+H152</f>
+        <v>17644008.236138448</v>
+      </c>
+      <c r="J22">
+        <f>H22+H43+H49+H53+H63+H66+H68+H78+H79+H86+H93+H94+H99+H100+H114+H122+H137+H171+H154</f>
+        <v>17019701.733017672</v>
+      </c>
+      <c r="K22">
+        <f>H53+H79+H88+H94+H99+H114+H152+H154+H171</f>
+        <v>2976273.2351659397</v>
+      </c>
+      <c r="L22">
+        <f>H86+H137+H171</f>
+        <v>905078.18882758496</v>
+      </c>
+      <c r="M22">
+        <f>H86</f>
+        <v>115122.754473693</v>
+      </c>
+      <c r="N22">
+        <f>H159</f>
+        <v>302072.55660798098</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>8.0293878053180592</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23">
+        <v>75.666570980687396</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23">
+        <v>132468.163528509</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>8.0902103547575699</v>
+      </c>
+      <c r="B24" t="s">
+        <v>226</v>
+      </c>
+      <c r="C24">
+        <v>71.206484441236398</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>227</v>
+      </c>
+      <c r="H24">
+        <v>12735.7141970995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>8.1536350298989095</v>
+      </c>
+      <c r="B25" t="s">
+        <v>274</v>
+      </c>
+      <c r="C25">
+        <v>78.382285295409105</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>156</v>
+      </c>
+      <c r="H25">
+        <v>7579.79267203581</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>8.2692867631624303</v>
+      </c>
+      <c r="B26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26">
+        <v>83.0794379185715</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26">
+        <v>17748.361236219898</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>8.3180558545224006</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27">
+        <v>90.9690796941766</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>110</v>
+      </c>
+      <c r="H27">
+        <v>50222.026403992197</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>8.3379370198277201</v>
+      </c>
+      <c r="B28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28">
+        <v>80.233975739387503</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>187</v>
+      </c>
+      <c r="H28">
+        <v>18155.654191129099</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>8.3880021361406207</v>
+      </c>
+      <c r="B29" t="s">
+        <v>201</v>
+      </c>
+      <c r="C29">
+        <v>81.755008823133295</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>202</v>
+      </c>
+      <c r="H29">
+        <v>15871.347320614001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>8.4699573179389596</v>
+      </c>
+      <c r="B30" t="s">
+        <v>260</v>
+      </c>
+      <c r="C30">
+        <v>83.286563397288703</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>261</v>
+      </c>
+      <c r="H30">
+        <v>10799.7242203356</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>8.5076529020684308</v>
+      </c>
+      <c r="B31" t="s">
+        <v>248</v>
+      </c>
+      <c r="C31">
+        <v>83.412415980722798</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31">
+        <v>11680.5326550917</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>8.6078902080839903</v>
+      </c>
+      <c r="B32" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32">
+        <v>78.216643199743999</v>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>159</v>
+      </c>
+      <c r="H32">
+        <v>3375.5886871338698</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>8.7023530074474902</v>
+      </c>
+      <c r="B33" t="s">
+        <v>253</v>
+      </c>
+      <c r="C33">
+        <v>81.556880977644298</v>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33">
+        <v>11140.6111035709</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>8.7192180620694995</v>
+      </c>
+      <c r="B34" t="s">
+        <v>236</v>
+      </c>
+      <c r="C34">
+        <v>71.977846627690496</v>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>100</v>
+      </c>
+      <c r="H34">
+        <v>12167.1087078085</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>8.7685238640945702</v>
+      </c>
+      <c r="B35" t="s">
+        <v>264</v>
+      </c>
+      <c r="C35">
+        <v>74.070729887399693</v>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>265</v>
+      </c>
+      <c r="H35">
+        <v>9890.1940928241693</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>8.7916382848967203</v>
+      </c>
+      <c r="B36" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36">
+        <v>92.702089256813096</v>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>98</v>
+      </c>
+      <c r="H36">
+        <v>60011.050902041803</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>8.8509708477544091</v>
+      </c>
+      <c r="B37" t="s">
+        <v>282</v>
+      </c>
+      <c r="C37">
+        <v>78.457522699800506</v>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
         <v>11</v>
       </c>
-      <c r="C3">
-        <v>96.278965728001594</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3">
-        <v>823778.97337447095</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>15.013722878434899</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4">
-        <v>91.142814938348494</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4">
-        <v>669644.77691929298</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>9.5564512669485797</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="H37">
+        <v>6333.6362592958603</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>8.9447590733776998</v>
+      </c>
+      <c r="B38" t="s">
+        <v>283</v>
+      </c>
+      <c r="C38">
+        <v>74.649849208976207</v>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>284</v>
+      </c>
+      <c r="H38">
+        <v>5839.4953735645004</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>9.0213104323111608</v>
+      </c>
+      <c r="B39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39">
+        <v>93.022616785071904</v>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>100</v>
+      </c>
+      <c r="H39">
+        <v>57811.658699866101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>9.10757684775594</v>
+      </c>
+      <c r="B40" t="s">
+        <v>198</v>
+      </c>
+      <c r="C40">
+        <v>80.295785099821501</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>177</v>
+      </c>
+      <c r="H40">
+        <v>16343.698791933601</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>9.1089548406179297</v>
+      </c>
+      <c r="B41" t="s">
+        <v>152</v>
+      </c>
+      <c r="C41">
+        <v>78.785976024168406</v>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>153</v>
+      </c>
+      <c r="H41">
+        <v>27298.4423808584</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>9.1398806832516204</v>
+      </c>
+      <c r="B42" t="s">
+        <v>199</v>
+      </c>
+      <c r="C42">
+        <v>86.988558167829495</v>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
+        <v>200</v>
+      </c>
+      <c r="H42">
+        <v>15931.5982336054</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>9.2296862494857805</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43">
+        <v>98.629706496315904</v>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
         <v>15</v>
       </c>
-      <c r="C5">
-        <v>99.050012820341493</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5">
-        <v>631962.61451091</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>13.720375473353201</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>96.322585730815803</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>605178.32783679396</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>9.2296862494857805</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>98.629706496315904</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7">
+      <c r="H43">
         <v>597066.96980136796</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>12.728796606709</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>95.808001683239695</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8">
-        <v>551212.03965080401</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>14.082482111214899</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9">
-        <v>88.051553401317094</v>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9">
-        <v>501986.68949736102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>12.084716107508299</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10">
-        <v>94.960123063347496</v>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10">
-        <v>418485.651543974</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>9.85294248224589</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11">
-        <v>98.551329906675093</v>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11">
-        <v>412496.07847163099</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>12.7885953862819</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12">
-        <v>97.013290493730096</v>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12">
-        <v>395358.45861314097</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>10.9970390679324</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13">
-        <v>89.423779677660306</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13">
-        <v>394381.45044526801</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>10.7284068068968</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14">
-        <v>98.229805038712101</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14">
-        <v>383968.05209737399</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>11.465407386451799</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15">
-        <v>90.207956351643304</v>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15">
-        <v>355383.19510815298</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>16.353955469231298</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16">
-        <v>94.918703250514994</v>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16">
-        <v>302072.55660798098</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>14.9754176217679</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17">
-        <v>80.284140464311506</v>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17">
-        <v>300135.233133192</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>12.387462201877501</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18">
-        <v>93.864025219451804</v>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18">
-        <v>220786.109694949</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>15.972004765723501</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19">
-        <v>85.0428570686272</v>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>39</v>
-      </c>
-      <c r="H19">
-        <v>217022.545470301</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>10.563042202035501</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20">
-        <v>97.589159336245203</v>
-      </c>
-      <c r="D20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20">
-        <v>187550.071788587</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>15.0331980344321</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21">
-        <v>78.437749742771302</v>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21">
-        <v>170728.07827035</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>14.0570257999277</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22">
-        <v>84.2207405926262</v>
-      </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22">
-        <v>163259.80421147199</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>16.063060793866899</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23">
-        <v>86.677885808107007</v>
-      </c>
-      <c r="D23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>46</v>
-      </c>
-      <c r="H23">
-        <v>154111.29887535999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>12.472356621966499</v>
-      </c>
-      <c r="B24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24">
-        <v>93.873666384500396</v>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H24">
-        <v>142073.440774324</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>14.9037206558523</v>
-      </c>
-      <c r="B25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25">
-        <v>82.424459768769196</v>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25">
-        <v>138093.51284795001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>8.0293878053180592</v>
-      </c>
-      <c r="B26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26">
-        <v>75.666570980687396</v>
-      </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26">
-        <v>132468.163528509</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>18.0140340784221</v>
-      </c>
-      <c r="B27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27">
-        <v>88.848454990420706</v>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>52</v>
-      </c>
-      <c r="H27">
-        <v>120310.65743459899</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>13.9499943821789</v>
-      </c>
-      <c r="B28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28">
-        <v>79.227563128031406</v>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>54</v>
-      </c>
-      <c r="H28">
-        <v>117475.830010787</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>11.926137269756101</v>
-      </c>
-      <c r="B29" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29">
-        <v>89.766109735058905</v>
-      </c>
-      <c r="D29" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>56</v>
-      </c>
-      <c r="H29">
-        <v>115122.754473693</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>11.0312295281733</v>
-      </c>
-      <c r="B30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30">
-        <v>73.4921532057528</v>
-      </c>
-      <c r="D30" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>58</v>
-      </c>
-      <c r="H30">
-        <v>110508.213682555</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>10.181545204642701</v>
-      </c>
-      <c r="B31" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31">
-        <v>94.500177342310394</v>
-      </c>
-      <c r="D31" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>60</v>
-      </c>
-      <c r="H31">
-        <v>105211.401042495</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>16.971534752194898</v>
-      </c>
-      <c r="B32" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32">
-        <v>77.178424003430607</v>
-      </c>
-      <c r="D32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
-        <v>62</v>
-      </c>
-      <c r="H32">
-        <v>103292.48215387001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>15.275822506154</v>
-      </c>
-      <c r="B33" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33">
-        <v>71.400213315774195</v>
-      </c>
-      <c r="D33" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" t="s">
-        <v>64</v>
-      </c>
-      <c r="H33">
-        <v>101187.506676693</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>13.3514733460666</v>
-      </c>
-      <c r="B34" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34">
-        <v>82.675313403732801</v>
-      </c>
-      <c r="D34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" t="s">
-        <v>66</v>
-      </c>
-      <c r="H34">
-        <v>99980.645467378796</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>13.1366237349781</v>
-      </c>
-      <c r="B35" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35">
-        <v>80.917181823038405</v>
-      </c>
-      <c r="D35" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H35">
-        <v>99819.883926172697</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>6.0113559101513303</v>
-      </c>
-      <c r="B36" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36">
-        <v>97.561169402453302</v>
-      </c>
-      <c r="D36" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>69</v>
-      </c>
-      <c r="H36">
-        <v>97958.357444017107</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>13.523348106516201</v>
-      </c>
-      <c r="B37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37">
-        <v>76.709822731750407</v>
-      </c>
-      <c r="D37" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" t="s">
-        <v>23</v>
-      </c>
-      <c r="H37">
-        <v>96893.6237674898</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>15.023316619352199</v>
-      </c>
-      <c r="B38" t="s">
-        <v>71</v>
-      </c>
-      <c r="C38">
-        <v>75.208481137986496</v>
-      </c>
-      <c r="D38" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" t="s">
-        <v>72</v>
-      </c>
-      <c r="H38">
-        <v>96484.136351083303</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>12.914730904326801</v>
-      </c>
-      <c r="B39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39">
-        <v>82.714366738753299</v>
-      </c>
-      <c r="D39" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
-        <v>74</v>
-      </c>
-      <c r="H39">
-        <v>90562.5295076443</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>15.868609003038699</v>
-      </c>
-      <c r="B40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40">
-        <v>91.414540832921304</v>
-      </c>
-      <c r="D40" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
-        <v>76</v>
-      </c>
-      <c r="H40">
-        <v>90232.208630877096</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>23.653009082440899</v>
-      </c>
-      <c r="B41" t="s">
-        <v>77</v>
-      </c>
-      <c r="C41">
-        <v>78.224165339802198</v>
-      </c>
-      <c r="D41" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
-        <v>78</v>
-      </c>
-      <c r="H41">
-        <v>79823.199970504793</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>20.286675565976999</v>
-      </c>
-      <c r="B42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42">
-        <v>87.718245578739001</v>
-      </c>
-      <c r="D42" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" t="s">
-        <v>80</v>
-      </c>
-      <c r="H42">
-        <v>79197.504832926104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>15.9661127816329</v>
-      </c>
-      <c r="B43" t="s">
-        <v>81</v>
-      </c>
-      <c r="C43">
-        <v>88.096891959837095</v>
-      </c>
-      <c r="D43" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" t="s">
-        <v>82</v>
-      </c>
-      <c r="H43">
-        <v>78311.543039553304</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J43">
+        <f>J22/I22</f>
+        <v>0.96461651486638555</v>
+      </c>
+      <c r="K43">
+        <f>K22/$I$22</f>
+        <v>0.16868464326999907</v>
+      </c>
+      <c r="L43">
+        <f t="shared" ref="L43:N43" si="0">L22/$I$22</f>
+        <v>5.1296631508808997E-2</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="0"/>
+        <v>6.5247506650953965E-3</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="0"/>
+        <v>1.7120404420877346E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>10.114618364801</v>
+        <v>9.2801652831168493</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="C44">
-        <v>92.569026973852004</v>
+        <v>70.322877166563998</v>
       </c>
       <c r="D44" t="b">
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>298</v>
       </c>
       <c r="H44">
-        <v>76228.153793290199</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3117.0511835720099</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>14.5505513065311</v>
+        <v>9.3729764256793597</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C45">
-        <v>73.645785472063196</v>
+        <v>85.142899971607605</v>
       </c>
       <c r="D45" t="b">
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="H45">
-        <v>76074.012580140305</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+        <v>52862.478468167799</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>11.398311448804</v>
+        <v>9.4291130944598098</v>
       </c>
       <c r="B46" t="s">
-        <v>86</v>
+        <v>239</v>
       </c>
       <c r="C46">
-        <v>80.601543828754501</v>
+        <v>86.014840970781606</v>
       </c>
       <c r="D46" t="b">
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="H46">
-        <v>71127.147259326899</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+        <v>12064.442529514001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>15.5149873086313</v>
+        <v>9.4913665705502392</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
+        <v>205</v>
       </c>
       <c r="C47">
-        <v>80.883088804377806</v>
+        <v>82.002236281779403</v>
       </c>
       <c r="D47" t="b">
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>89</v>
+        <v>206</v>
       </c>
       <c r="H47">
-        <v>68766.030900024096</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+        <v>15486.074282969401</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>5.37273448999093</v>
+        <v>9.4916059342218109</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="C48">
-        <v>90.416773671599202</v>
+        <v>80.442558024841503</v>
       </c>
       <c r="D48" t="b">
         <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>208</v>
       </c>
       <c r="H48">
-        <v>65357.922859203703</v>
+        <v>15486.074282969401</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>13.858064869938801</v>
+        <v>9.5564512669485797</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="C49">
-        <v>71.934483510014601</v>
+        <v>99.050012820341493</v>
       </c>
       <c r="D49" t="b">
         <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="H49">
-        <v>64876.118765686202</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+        <v>631962.61451091</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>11.6172161467303</v>
+        <v>9.6357255930062404</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>147</v>
       </c>
       <c r="C50">
-        <v>92.0980761445892</v>
+        <v>82.871564774421699</v>
       </c>
       <c r="D50" t="b">
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H50">
-        <v>62310.480085619398</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+        <v>29104.1738035979</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>6.7878696891479704</v>
+        <v>9.7067951640661398</v>
       </c>
       <c r="B51" t="s">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="C51">
-        <v>80.116289290942007</v>
+        <v>75.957082353015494</v>
       </c>
       <c r="D51" t="b">
         <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="H51">
-        <v>61737.255655543297</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+        <v>12596.938931062001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>14.3884456091094</v>
+        <v>9.7931123720845008</v>
       </c>
       <c r="B52" t="s">
-        <v>96</v>
+        <v>262</v>
       </c>
       <c r="C52">
-        <v>78.350568225563705</v>
+        <v>74.200006869549895</v>
       </c>
       <c r="D52" t="b">
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>14</v>
+        <v>263</v>
       </c>
       <c r="H52">
-        <v>60044.4213425747</v>
+        <v>1147.4035733337801</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>14.3889001651721</v>
+        <v>9.85294248224589</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="C53">
-        <v>77.804284869065299</v>
+        <v>98.551329906675093</v>
       </c>
       <c r="D53" t="b">
         <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H53">
-        <v>60044.4213425747</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+        <v>412496.07847163099</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>8.7916382848967203</v>
+        <v>9.9443386253772097</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>237</v>
       </c>
       <c r="C54">
-        <v>92.702089256813096</v>
+        <v>77.272129673343898</v>
       </c>
       <c r="D54" t="b">
         <v>1</v>
       </c>
       <c r="E54" t="s">
-        <v>99</v>
+        <v>238</v>
       </c>
       <c r="H54">
-        <v>60011.050902041803</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+        <v>12119.1349764143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>9.0213104323111608</v>
+        <v>9.9521455316233602</v>
       </c>
       <c r="B55" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="C55">
-        <v>93.022616785071904</v>
+        <v>77.737590000897598</v>
       </c>
       <c r="D55" t="b">
         <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H55">
-        <v>57811.658699866101</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+        <v>25389.853421383501</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>6.7367122934712604</v>
+        <v>10.0214933680175</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="C56">
-        <v>90.692259515772307</v>
+        <v>70.531031531459803</v>
       </c>
       <c r="D56" t="b">
         <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="H56">
-        <v>57727.953314653198</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+        <v>12397.698391735101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>5.3766850903912999</v>
+        <v>10.06747797635</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="C57">
-        <v>87.963176399796595</v>
+        <v>72.2521546170927</v>
       </c>
       <c r="D57" t="b">
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="H57">
-        <v>54152.145098895198</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+        <v>25138.6521230037</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>9.3729764256793597</v>
+        <v>10.114618364801</v>
       </c>
       <c r="B58" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C58">
-        <v>85.142899971607605</v>
+        <v>92.569026973852004</v>
       </c>
       <c r="D58" t="b">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="H58">
-        <v>52862.478468167799</v>
+        <v>76228.153793290199</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>20.6217099453293</v>
+        <v>10.181545204642701</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="C59">
-        <v>92.165932300632207</v>
+        <v>94.500177342310394</v>
       </c>
       <c r="D59" t="b">
         <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="H59">
-        <v>52295.123441220399</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+        <v>105211.401042495</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>11.3249865513181</v>
+        <v>10.2103804193997</v>
       </c>
       <c r="B60" t="s">
-        <v>55</v>
+        <v>278</v>
       </c>
       <c r="C60">
-        <v>86.799028176968406</v>
+        <v>76.447277261543107</v>
       </c>
       <c r="D60" t="b">
         <v>1</v>
       </c>
       <c r="E60" t="s">
-        <v>56</v>
+        <v>279</v>
       </c>
       <c r="H60">
-        <v>51640.170860000697</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+        <v>6958.0602113640098</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>8.3180558545224006</v>
+        <v>10.3054375133703</v>
       </c>
       <c r="B61" t="s">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="C61">
-        <v>90.9690796941766</v>
+        <v>76.735692309060099</v>
       </c>
       <c r="D61" t="b">
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>111</v>
+        <v>220</v>
       </c>
       <c r="H61">
-        <v>50222.026403992197</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+        <v>14414.0117050636</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>11.256866590795299</v>
+        <v>10.550922874941</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="C62">
-        <v>86.536399298525296</v>
+        <v>73.232393611137397</v>
       </c>
       <c r="D62" t="b">
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H62">
-        <v>49669.1240596219</v>
+        <v>12928.8274289602</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>18.557818392862998</v>
+        <v>10.563042202035501</v>
       </c>
       <c r="B63" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="C63">
-        <v>91.4008299054465</v>
+        <v>97.589159336245203</v>
       </c>
       <c r="D63" t="b">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="H63">
-        <v>48825.957611390302</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+        <v>187550.071788587</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>12.159274852275001</v>
+        <v>10.580032690739801</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>196</v>
       </c>
       <c r="C64">
-        <v>85.871400792939895</v>
+        <v>73.006107539728902</v>
       </c>
       <c r="D64" t="b">
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="H64">
-        <v>48193.385892635903</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+        <v>16722.670614422401</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>12.154638755431099</v>
+        <v>10.6234630464558</v>
       </c>
       <c r="B65" t="s">
-        <v>116</v>
+        <v>262</v>
       </c>
       <c r="C65">
-        <v>76.599610322368605</v>
+        <v>73.221934745095496</v>
       </c>
       <c r="D65" t="b">
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>117</v>
+        <v>263</v>
       </c>
       <c r="H65">
-        <v>48193.385892635903</v>
+        <v>3853.8320637223801</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>18.790684130648501</v>
+        <v>10.7284068068968</v>
       </c>
       <c r="B66" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="C66">
-        <v>70.047855590456095</v>
+        <v>98.229805038712101</v>
       </c>
       <c r="D66" t="b">
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="H66">
-        <v>47783.047712384403</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+        <v>383968.05209737399</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>13.0179949608115</v>
+        <v>10.834851823410499</v>
       </c>
       <c r="B67" t="s">
-        <v>120</v>
+        <v>228</v>
       </c>
       <c r="C67">
-        <v>82.253835019348003</v>
+        <v>85.441410192425593</v>
       </c>
       <c r="D67" t="b">
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>121</v>
+        <v>229</v>
       </c>
       <c r="H67">
-        <v>47089.4194560084</v>
+        <v>12666.052171236401</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>14.495817535788399</v>
+        <v>10.9970390679324</v>
       </c>
       <c r="B68" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="C68">
-        <v>76.831083997096499</v>
+        <v>89.423779677660306</v>
       </c>
       <c r="D68" t="b">
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H68">
-        <v>44920.636882905601</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+        <v>394381.45044526801</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>11.8390682119754</v>
+        <v>11.0312295281733</v>
       </c>
       <c r="B69" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C69">
-        <v>71.190344621484698</v>
+        <v>73.4921532057528</v>
       </c>
       <c r="D69" t="b">
         <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="H69">
-        <v>43843.966568616997</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+        <v>110508.213682555</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>11.7199896455827</v>
+        <v>11.0631142958211</v>
       </c>
       <c r="B70" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="C70">
-        <v>77.889046740548594</v>
+        <v>74.575934501339802</v>
       </c>
       <c r="D70" t="b">
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="H70">
-        <v>43731.402731864298</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+        <v>24401.593574081398</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>16.683752535158199</v>
+        <v>11.182923101015399</v>
       </c>
       <c r="B71" t="s">
-        <v>127</v>
+        <v>262</v>
       </c>
       <c r="C71">
-        <v>70.836745584762397</v>
+        <v>78.130737965002297</v>
       </c>
       <c r="D71" t="b">
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>46</v>
+        <v>263</v>
       </c>
       <c r="H71">
-        <v>38210.3593421279</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10025.617369359499</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>12.1475882756377</v>
+        <v>11.191947982836901</v>
       </c>
       <c r="B72" t="s">
+        <v>39</v>
+      </c>
+      <c r="C72">
+        <v>83.357987067363794</v>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" t="s">
+        <v>29</v>
+      </c>
+      <c r="H72">
+        <v>29916.7316171366</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>11.191947982836901</v>
+      </c>
+      <c r="B73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73">
+        <v>80.662819531571898</v>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
+        <v>29</v>
+      </c>
+      <c r="H73">
+        <v>29916.7316171366</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>11.256866590795299</v>
+      </c>
+      <c r="B74" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74">
+        <v>86.536399298525296</v>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74">
+        <v>49669.1240596219</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>11.3249865513181</v>
+      </c>
+      <c r="B75" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75">
+        <v>86.799028176968406</v>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
         <v>55</v>
       </c>
-      <c r="C72">
-        <v>79.423148251996807</v>
-      </c>
-      <c r="D72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" t="s">
-        <v>56</v>
-      </c>
-      <c r="H72">
-        <v>37299.331123252203</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>17.460976987465401</v>
-      </c>
-      <c r="B73" t="s">
-        <v>128</v>
-      </c>
-      <c r="C73">
-        <v>73.053474095102899</v>
-      </c>
-      <c r="D73" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" t="s">
-        <v>52</v>
-      </c>
-      <c r="H73">
-        <v>36668.180313255201</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>12.518138800139599</v>
-      </c>
-      <c r="B74" t="s">
-        <v>129</v>
-      </c>
-      <c r="C74">
-        <v>72.148122884916305</v>
-      </c>
-      <c r="D74" t="b">
-        <v>1</v>
-      </c>
-      <c r="E74" t="s">
-        <v>130</v>
-      </c>
-      <c r="H74">
-        <v>36341.245194302399</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>7.7601624677887102</v>
-      </c>
-      <c r="B75" t="s">
-        <v>131</v>
-      </c>
-      <c r="C75">
-        <v>90.510368916000104</v>
-      </c>
-      <c r="D75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" t="s">
-        <v>12</v>
-      </c>
       <c r="H75">
-        <v>34902.493095443097</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+        <v>51640.170860000697</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>6.8368060723470601</v>
+        <v>11.398311448804</v>
       </c>
       <c r="B76" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="C76">
-        <v>88.560790370128899</v>
+        <v>80.601543828754501</v>
       </c>
       <c r="D76" t="b">
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="H76">
-        <v>34740.820103188598</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+        <v>71127.147259326899</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>11.410406702392301</v>
       </c>
       <c r="B77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C77">
         <v>79.793204136348095</v>
@@ -3370,7 +3474,7 @@
         <v>1</v>
       </c>
       <c r="E77" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H77">
         <v>34499.1473809003</v>
@@ -3378,590 +3482,590 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>15.894453869287201</v>
+        <v>11.4526922770967</v>
       </c>
       <c r="B78" t="s">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="C78">
-        <v>84.554816095486302</v>
+        <v>96.278965728001594</v>
       </c>
       <c r="D78" t="b">
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>135</v>
+        <v>11</v>
       </c>
       <c r="H78">
-        <v>34293.063933993697</v>
+        <v>823778.97337447095</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>18.187472053170001</v>
+        <v>11.465407386451799</v>
       </c>
       <c r="B79" t="s">
-        <v>136</v>
+        <v>31</v>
       </c>
       <c r="C79">
-        <v>80.665879896190503</v>
+        <v>90.207956351643304</v>
       </c>
       <c r="D79" t="b">
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>137</v>
+        <v>22</v>
       </c>
       <c r="H79">
-        <v>33774.877500791401</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+        <v>355383.19510815298</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>17.379330463588399</v>
+        <v>11.6172161467303</v>
       </c>
       <c r="B80" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="C80">
-        <v>71.851648819238207</v>
+        <v>92.0980761445892</v>
       </c>
       <c r="D80" t="b">
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
       <c r="H80">
-        <v>32943.578547569603</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+        <v>62310.480085619398</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>17.119869910738501</v>
+        <v>11.706060929721801</v>
       </c>
       <c r="B81" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="C81">
-        <v>72.734854128060107</v>
+        <v>85.3611001006755</v>
       </c>
       <c r="D81" t="b">
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="H81">
-        <v>30457.432673862699</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+        <v>23534.456924034599</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>13.2655442209265</v>
+        <v>11.7199896455827</v>
       </c>
       <c r="B82" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="C82">
-        <v>75.673710486451995</v>
+        <v>77.889046740548594</v>
       </c>
       <c r="D82" t="b">
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="H82">
-        <v>30169.467286589901</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+        <v>43731.402731864298</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>11.191947982836901</v>
+        <v>11.7641824126081</v>
       </c>
       <c r="B83" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C83">
-        <v>83.357987067363794</v>
+        <v>80.510321917445395</v>
       </c>
       <c r="D83" t="b">
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H83">
-        <v>29916.7316171366</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4215.8835830804201</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>11.191947982836901</v>
+        <v>11.833500458229601</v>
       </c>
       <c r="B84" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="C84">
-        <v>80.662819531571898</v>
+        <v>75.333598259274098</v>
       </c>
       <c r="D84" t="b">
         <v>1</v>
       </c>
       <c r="E84" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H84">
-        <v>29916.7316171366</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26913.199174430301</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>19.039036337118599</v>
+        <v>11.8390682119754</v>
       </c>
       <c r="B85" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="C85">
-        <v>75.551320034241598</v>
+        <v>71.190344621484698</v>
       </c>
       <c r="D85" t="b">
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="H85">
-        <v>29744.822501987899</v>
+        <v>43843.966568616997</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>3.1799054323826201</v>
+        <v>11.926137269756101</v>
       </c>
       <c r="B86" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="C86">
-        <v>89.212334563582701</v>
+        <v>89.766109735058905</v>
       </c>
       <c r="D86" t="b">
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>147</v>
+        <v>55</v>
       </c>
       <c r="H86">
-        <v>29375.767883561799</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+        <v>115122.754473693</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>9.6357255930062404</v>
+        <v>11.9346012791465</v>
       </c>
       <c r="B87" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="C87">
-        <v>82.871564774421699</v>
+        <v>79.218495639884907</v>
       </c>
       <c r="D87" t="b">
         <v>1</v>
       </c>
       <c r="E87" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="H87">
-        <v>29104.1738035979</v>
+        <v>20907.264062485701</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>16.141199438623801</v>
+        <v>12.084716107508299</v>
       </c>
       <c r="B88" t="s">
-        <v>149</v>
+        <v>23</v>
       </c>
       <c r="C88">
-        <v>77.845093530776893</v>
+        <v>94.960123063347496</v>
       </c>
       <c r="D88" t="b">
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="H88">
-        <v>28723.119222507899</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+        <v>418485.651543974</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>13.2104666712357</v>
+        <v>12.1073475677548</v>
       </c>
       <c r="B89" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="C89">
-        <v>78.585580578912399</v>
+        <v>79.274444676042904</v>
       </c>
       <c r="D89" t="b">
         <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="H89">
-        <v>28103.986553491701</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+        <v>23017.806720568798</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>9.1089548406179297</v>
+        <v>12.1475882756377</v>
       </c>
       <c r="B90" t="s">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="C90">
-        <v>78.785976024168406</v>
+        <v>79.423148251996807</v>
       </c>
       <c r="D90" t="b">
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="H90">
-        <v>27298.4423808584</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+        <v>37299.331123252203</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>11.833500458229601</v>
+        <v>12.154638755431099</v>
       </c>
       <c r="B91" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="C91">
-        <v>75.333598259274098</v>
+        <v>76.599610322368605</v>
       </c>
       <c r="D91" t="b">
         <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="H91">
-        <v>26913.199174430301</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+        <v>48193.385892635903</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>4.23448639810759</v>
+        <v>12.159274852275001</v>
       </c>
       <c r="B92" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="C92">
-        <v>88.139288707531605</v>
+        <v>85.871400792939895</v>
       </c>
       <c r="D92" t="b">
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="H92">
-        <v>26789.263654456001</v>
+        <v>48193.385892635903</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>9.9521455316233602</v>
+        <v>12.387462201877501</v>
       </c>
       <c r="B93" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
       <c r="C93">
-        <v>77.737590000897598</v>
+        <v>93.864025219451804</v>
       </c>
       <c r="D93" t="b">
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H93">
-        <v>25389.853421383501</v>
+        <v>220786.109694949</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>17.572997416703501</v>
+        <v>12.472356621966499</v>
       </c>
       <c r="B94" t="s">
-        <v>138</v>
+        <v>46</v>
       </c>
       <c r="C94">
-        <v>81.0582416444757</v>
+        <v>93.873666384500396</v>
       </c>
       <c r="D94" t="b">
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="H94">
-        <v>25231.3539607046</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+        <v>142073.440774324</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>10.06747797635</v>
+        <v>12.4830241598954</v>
       </c>
       <c r="B95" t="s">
-        <v>159</v>
+        <v>19</v>
       </c>
       <c r="C95">
-        <v>72.2521546170927</v>
+        <v>75.912887085708206</v>
       </c>
       <c r="D95" t="b">
         <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="H95">
-        <v>25138.6521230037</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+        <v>14469.4102987305</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>11.0631142958211</v>
+        <v>12.518138800139599</v>
       </c>
       <c r="B96" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="C96">
-        <v>74.575934501339802</v>
+        <v>72.148122884916305</v>
       </c>
       <c r="D96" t="b">
         <v>1</v>
       </c>
       <c r="E96" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="H96">
-        <v>24401.593574081398</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+        <v>36341.245194302399</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>14.700903952670499</v>
+        <v>12.5805285874885</v>
       </c>
       <c r="B97" t="s">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="C97">
-        <v>70.6732907349882</v>
+        <v>76.936472451412101</v>
       </c>
       <c r="D97" t="b">
         <v>1</v>
       </c>
       <c r="E97" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H97">
-        <v>23729.601515942501</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+        <v>20674.537259642901</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>11.706060929721801</v>
+        <v>12.7024210276931</v>
       </c>
       <c r="B98" t="s">
-        <v>163</v>
+        <v>290</v>
       </c>
       <c r="C98">
-        <v>85.3611001006755</v>
+        <v>71.437966117276005</v>
       </c>
       <c r="D98" t="b">
         <v>1</v>
       </c>
       <c r="E98" t="s">
-        <v>164</v>
+        <v>51</v>
       </c>
       <c r="H98">
-        <v>23534.456924034599</v>
+        <v>3639.1609586670502</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>7.7565122990738704</v>
+        <v>12.728796606709</v>
       </c>
       <c r="B99" t="s">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="C99">
-        <v>70.558911824126497</v>
+        <v>95.808001683239695</v>
       </c>
       <c r="D99" t="b">
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="H99">
-        <v>23247.744464137599</v>
+        <v>551212.03965080401</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>12.1073475677548</v>
+        <v>12.7885953862819</v>
       </c>
       <c r="B100" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="C100">
-        <v>79.274444676042904</v>
+        <v>97.013290493730096</v>
       </c>
       <c r="D100" t="b">
         <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="H100">
-        <v>23017.806720568798</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+        <v>395358.45861314097</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>13.9018707302914</v>
+        <v>12.914730904326801</v>
       </c>
       <c r="B101" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="C101">
-        <v>76.576386247851204</v>
+        <v>82.714366738753299</v>
       </c>
       <c r="D101" t="b">
         <v>1</v>
       </c>
       <c r="E101" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="H101">
-        <v>22968.2129977146</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+        <v>90562.5295076443</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>15.854133476513899</v>
+        <v>13.0179949608115</v>
       </c>
       <c r="B102" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="C102">
-        <v>79.035805620921295</v>
+        <v>82.253835019348003</v>
       </c>
       <c r="D102" t="b">
         <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="H102">
-        <v>22890.150485006001</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+        <v>47089.4194560084</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>17.0460603414075</v>
+        <v>13.0849246818774</v>
       </c>
       <c r="B103" t="s">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="C103">
-        <v>72.846970594556893</v>
+        <v>71.734568638020804</v>
       </c>
       <c r="D103" t="b">
         <v>1</v>
       </c>
       <c r="E103" t="s">
+        <v>65</v>
+      </c>
+      <c r="H103">
+        <v>14392.5772729491</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>13.1366237349781</v>
+      </c>
+      <c r="B104" t="s">
+        <v>66</v>
+      </c>
+      <c r="C104">
+        <v>80.917181823038405</v>
+      </c>
+      <c r="D104" t="b">
+        <v>1</v>
+      </c>
+      <c r="E104" t="s">
+        <v>65</v>
+      </c>
+      <c r="H104">
+        <v>99819.883926172697</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>13.2104666712357</v>
+      </c>
+      <c r="B105" t="s">
+        <v>150</v>
+      </c>
+      <c r="C105">
+        <v>78.585580578912399</v>
+      </c>
+      <c r="D105" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" t="s">
+        <v>151</v>
+      </c>
+      <c r="H105">
+        <v>28103.986553491701</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>13.2655442209265</v>
+      </c>
+      <c r="B106" t="s">
         <v>141</v>
       </c>
-      <c r="H103">
-        <v>21834.2032741107</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <v>11.9346012791465</v>
-      </c>
-      <c r="B104" t="s">
-        <v>125</v>
-      </c>
-      <c r="C104">
-        <v>79.218495639884907</v>
-      </c>
-      <c r="D104" t="b">
-        <v>1</v>
-      </c>
-      <c r="E104" t="s">
-        <v>126</v>
-      </c>
-      <c r="H104">
-        <v>20907.264062485701</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <v>12.5805285874885</v>
-      </c>
-      <c r="B105" t="s">
-        <v>173</v>
-      </c>
-      <c r="C105">
-        <v>76.936472451412101</v>
-      </c>
-      <c r="D105" t="b">
-        <v>1</v>
-      </c>
-      <c r="E105" t="s">
-        <v>25</v>
-      </c>
-      <c r="H105">
-        <v>20674.537259642901</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <v>17.217928040709001</v>
-      </c>
-      <c r="B106" t="s">
-        <v>138</v>
-      </c>
       <c r="C106">
-        <v>88.650117466340205</v>
+        <v>75.673710486451995</v>
       </c>
       <c r="D106" t="b">
         <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H106">
-        <v>20459.410012548698</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+        <v>30169.467286589901</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>13.3019826320467</v>
       </c>
       <c r="B107" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C107">
         <v>83.602605927369794</v>
@@ -3970,258 +4074,258 @@
         <v>1</v>
       </c>
       <c r="E107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H107">
         <v>20238.182803375901</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>14.2468383073194</v>
+        <v>13.3324538657485</v>
       </c>
       <c r="B108" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C108">
-        <v>77.970954085365605</v>
+        <v>70.518973825324196</v>
       </c>
       <c r="D108" t="b">
         <v>1</v>
       </c>
       <c r="E108" t="s">
-        <v>107</v>
+        <v>204</v>
       </c>
       <c r="H108">
-        <v>20034.579979451399</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+        <v>15660.4061242755</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>5.7559266958886504</v>
+        <v>13.3514733460666</v>
       </c>
       <c r="B109" t="s">
-        <v>177</v>
+        <v>64</v>
       </c>
       <c r="C109">
-        <v>88.989662979746498</v>
+        <v>82.675313403732801</v>
       </c>
       <c r="D109" t="b">
         <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="H109">
-        <v>19988.389436862599</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+        <v>99980.645467378796</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>15.878453999887</v>
+        <v>13.4724678053161</v>
       </c>
       <c r="B110" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C110">
-        <v>74.338510383767002</v>
+        <v>70.004039378106796</v>
       </c>
       <c r="D110" t="b">
         <v>1</v>
       </c>
       <c r="E110" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="H110">
-        <v>19785.735425794701</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8694.6170693972399</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>4.2393737685011903</v>
+        <v>13.523348106516201</v>
       </c>
       <c r="B111" t="s">
-        <v>181</v>
+        <v>69</v>
       </c>
       <c r="C111">
-        <v>75.989414880563402</v>
+        <v>76.709822731750407</v>
       </c>
       <c r="D111" t="b">
         <v>1</v>
       </c>
       <c r="E111" t="s">
-        <v>182</v>
+        <v>22</v>
       </c>
       <c r="H111">
-        <v>19150.127014097299</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+        <v>96893.6237674898</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>26.849380013378202</v>
+        <v>13.596801003430601</v>
       </c>
       <c r="B112" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C112">
-        <v>70.378187236064804</v>
+        <v>71.476885195867396</v>
       </c>
       <c r="D112" t="b">
         <v>1</v>
       </c>
       <c r="E112" t="s">
+        <v>185</v>
+      </c>
+      <c r="H112">
+        <v>10606.7626845594</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>13.641833802631901</v>
+      </c>
+      <c r="B113" t="s">
         <v>184</v>
       </c>
-      <c r="H112">
-        <v>18820.969408996702</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113">
-        <v>17.509958413433601</v>
-      </c>
-      <c r="B113" t="s">
-        <v>138</v>
-      </c>
       <c r="C113">
-        <v>79.227968777130698</v>
+        <v>76.780588243576005</v>
       </c>
       <c r="D113" t="b">
         <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="H113">
-        <v>18789.2614993641</v>
+        <v>18376.837698749299</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>13.641833802631901</v>
+        <v>13.720375473353201</v>
       </c>
       <c r="B114" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="C114">
-        <v>76.780588243576005</v>
+        <v>96.322585730815803</v>
       </c>
       <c r="D114" t="b">
         <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>186</v>
+        <v>17</v>
       </c>
       <c r="H114">
-        <v>18376.837698749299</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+        <v>605178.32783679396</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>8.3379370198277201</v>
+        <v>13.858064869938801</v>
       </c>
       <c r="B115" t="s">
-        <v>187</v>
+        <v>91</v>
       </c>
       <c r="C115">
-        <v>80.233975739387503</v>
+        <v>71.934483510014601</v>
       </c>
       <c r="D115" t="b">
         <v>1</v>
       </c>
       <c r="E115" t="s">
-        <v>188</v>
+        <v>92</v>
       </c>
       <c r="H115">
-        <v>18155.654191129099</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+        <v>64876.118765686202</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>7.8295239439419202</v>
+        <v>13.9018707302914</v>
       </c>
       <c r="B116" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="C116">
-        <v>82.601815731963299</v>
+        <v>76.576386247851204</v>
       </c>
       <c r="D116" t="b">
         <v>1</v>
       </c>
       <c r="E116" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="H116">
-        <v>18126.656668075299</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+        <v>22968.2129977146</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>19.1455072754427</v>
+        <v>13.9499943821789</v>
       </c>
       <c r="B117" t="s">
-        <v>190</v>
+        <v>52</v>
       </c>
       <c r="C117">
-        <v>72.808943869243194</v>
+        <v>79.227563128031406</v>
       </c>
       <c r="D117" t="b">
         <v>1</v>
       </c>
       <c r="E117" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="H117">
-        <v>18051.7034934365</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+        <v>117475.830010787</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>14.4319743358634</v>
+        <v>13.9723662292801</v>
       </c>
       <c r="B118" t="s">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="C118">
-        <v>76.432266418003707</v>
+        <v>72.049841730564495</v>
       </c>
       <c r="D118" t="b">
         <v>1</v>
       </c>
       <c r="E118" t="s">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="H118">
-        <v>17858.165111877301</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10899.2449939985</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>8.2692867631624303</v>
+        <v>13.972604279494499</v>
       </c>
       <c r="B119" t="s">
-        <v>95</v>
+        <v>258</v>
       </c>
       <c r="C119">
-        <v>83.0794379185715</v>
+        <v>75.120703068220607</v>
       </c>
       <c r="D119" t="b">
         <v>1</v>
       </c>
       <c r="E119" t="s">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="H119">
-        <v>17748.361236219898</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10899.2449939985</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>14.0520140341381</v>
       </c>
       <c r="B120" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C120">
         <v>71.073860934627106</v>
@@ -4230,198 +4334,198 @@
         <v>1</v>
       </c>
       <c r="E120" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H120">
         <v>17587.082529815201</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>14.603923618328</v>
+        <v>14.0570257999277</v>
       </c>
       <c r="B121" t="s">
-        <v>194</v>
+        <v>42</v>
       </c>
       <c r="C121">
-        <v>73.683796906180405</v>
+        <v>84.2207405926262</v>
       </c>
       <c r="D121" t="b">
         <v>1</v>
       </c>
       <c r="E121" t="s">
-        <v>195</v>
+        <v>43</v>
       </c>
       <c r="H121">
-        <v>17171.662436779199</v>
+        <v>163259.80421147199</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>18.389159236756001</v>
+        <v>14.082482111214899</v>
       </c>
       <c r="B122" t="s">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="C122">
-        <v>76.477574428347594</v>
+        <v>88.051553401317094</v>
       </c>
       <c r="D122" t="b">
         <v>1</v>
       </c>
       <c r="E122" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="H122">
-        <v>16949.220953733598</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+        <v>501986.68949736102</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>10.580032690739801</v>
+        <v>14.1666048515771</v>
       </c>
       <c r="B123" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="C123">
-        <v>73.006107539728902</v>
+        <v>71.444776516372301</v>
       </c>
       <c r="D123" t="b">
         <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="H123">
-        <v>16722.670614422401</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+        <v>11871.782200788601</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>9.10757684775594</v>
+        <v>14.2468383073194</v>
       </c>
       <c r="B124" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="C124">
-        <v>80.295785099821501</v>
+        <v>77.970954085365605</v>
       </c>
       <c r="D124" t="b">
         <v>1</v>
       </c>
       <c r="E124" t="s">
-        <v>178</v>
+        <v>106</v>
       </c>
       <c r="H124">
-        <v>16343.698791933601</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+        <v>20034.579979451399</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>9.1398806832516204</v>
+        <v>14.337633153981299</v>
       </c>
       <c r="B125" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="C125">
-        <v>86.988558167829495</v>
+        <v>72.6758392490039</v>
       </c>
       <c r="D125" t="b">
         <v>1</v>
       </c>
       <c r="E125" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="H125">
-        <v>15931.5982336054</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+        <v>11894.2926352226</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>8.3880021361406207</v>
+        <v>14.3884456091094</v>
       </c>
       <c r="B126" t="s">
-        <v>202</v>
+        <v>95</v>
       </c>
       <c r="C126">
-        <v>81.755008823133295</v>
+        <v>78.350568225563705</v>
       </c>
       <c r="D126" t="b">
         <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="H126">
-        <v>15871.347320614001</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+        <v>60044.4213425747</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>13.3324538657485</v>
+        <v>14.3889001651721</v>
       </c>
       <c r="B127" t="s">
-        <v>204</v>
+        <v>96</v>
       </c>
       <c r="C127">
-        <v>70.518973825324196</v>
+        <v>77.804284869065299</v>
       </c>
       <c r="D127" t="b">
         <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>205</v>
+        <v>13</v>
       </c>
       <c r="H127">
-        <v>15660.4061242755</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+        <v>60044.4213425747</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>9.4913665705502392</v>
+        <v>14.4319743358634</v>
       </c>
       <c r="B128" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="C128">
-        <v>82.002236281779403</v>
+        <v>76.432266418003707</v>
       </c>
       <c r="D128" t="b">
         <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="H128">
-        <v>15486.074282969401</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+        <v>17858.165111877301</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>9.4916059342218109</v>
+        <v>14.495817535788399</v>
       </c>
       <c r="B129" t="s">
-        <v>208</v>
+        <v>121</v>
       </c>
       <c r="C129">
-        <v>80.442558024841503</v>
+        <v>76.831083997096499</v>
       </c>
       <c r="D129" t="b">
         <v>1</v>
       </c>
       <c r="E129" t="s">
-        <v>209</v>
+        <v>41</v>
       </c>
       <c r="H129">
-        <v>15486.074282969401</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+        <v>44920.636882905601</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>14.5162813031759</v>
       </c>
       <c r="B130" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C130">
         <v>76.742326907128401</v>
@@ -4430,1198 +4534,1198 @@
         <v>1</v>
       </c>
       <c r="E130" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H130">
         <v>15057.653945296001</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
+        <v>14.5505513065311</v>
+      </c>
+      <c r="B131" t="s">
+        <v>83</v>
+      </c>
+      <c r="C131">
+        <v>73.645785472063196</v>
+      </c>
+      <c r="D131" t="b">
+        <v>1</v>
+      </c>
+      <c r="E131" t="s">
+        <v>84</v>
+      </c>
+      <c r="H131">
+        <v>76074.012580140305</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>14.603923618328</v>
+      </c>
+      <c r="B132" t="s">
+        <v>193</v>
+      </c>
+      <c r="C132">
+        <v>73.683796906180405</v>
+      </c>
+      <c r="D132" t="b">
+        <v>1</v>
+      </c>
+      <c r="E132" t="s">
+        <v>194</v>
+      </c>
+      <c r="H132">
+        <v>17171.662436779199</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>14.700903952670499</v>
+      </c>
+      <c r="B133" t="s">
+        <v>19</v>
+      </c>
+      <c r="C133">
+        <v>70.6732907349882</v>
+      </c>
+      <c r="D133" t="b">
+        <v>1</v>
+      </c>
+      <c r="E133" t="s">
+        <v>20</v>
+      </c>
+      <c r="H133">
+        <v>23729.601515942501</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A134">
         <v>14.827630486071699</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B134" t="s">
+        <v>211</v>
+      </c>
+      <c r="C134">
+        <v>74.491895522778094</v>
+      </c>
+      <c r="D134" t="b">
+        <v>1</v>
+      </c>
+      <c r="E134" t="s">
         <v>212</v>
       </c>
-      <c r="C131">
-        <v>74.491895522778094</v>
-      </c>
-      <c r="D131" t="b">
-        <v>1</v>
-      </c>
-      <c r="E131" t="s">
-        <v>213</v>
-      </c>
-      <c r="H131">
+      <c r="H134">
         <v>14900.806515865201</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132">
-        <v>22.802954475199599</v>
-      </c>
-      <c r="B132" t="s">
-        <v>214</v>
-      </c>
-      <c r="C132">
-        <v>79.813639162276303</v>
-      </c>
-      <c r="D132" t="b">
-        <v>1</v>
-      </c>
-      <c r="E132" t="s">
-        <v>215</v>
-      </c>
-      <c r="H132">
-        <v>14686.690376365401</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133">
-        <v>16.1080021087195</v>
-      </c>
-      <c r="B133" t="s">
-        <v>216</v>
-      </c>
-      <c r="C133">
-        <v>76.120558884048805</v>
-      </c>
-      <c r="D133" t="b">
-        <v>1</v>
-      </c>
-      <c r="E133" t="s">
-        <v>217</v>
-      </c>
-      <c r="H133">
-        <v>14591.932970681401</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134">
-        <v>12.4830241598954</v>
-      </c>
-      <c r="B134" t="s">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>14.9037206558523</v>
+      </c>
+      <c r="B135" t="s">
+        <v>19</v>
+      </c>
+      <c r="C135">
+        <v>82.424459768769196</v>
+      </c>
+      <c r="D135" t="b">
+        <v>1</v>
+      </c>
+      <c r="E135" t="s">
         <v>20</v>
       </c>
-      <c r="C134">
-        <v>75.912887085708206</v>
-      </c>
-      <c r="D134" t="b">
-        <v>1</v>
-      </c>
-      <c r="E134" t="s">
-        <v>21</v>
-      </c>
-      <c r="H134">
-        <v>14469.4102987305</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135">
-        <v>7.1541843982103597</v>
-      </c>
-      <c r="B135" t="s">
-        <v>218</v>
-      </c>
-      <c r="C135">
-        <v>85.193960490128703</v>
-      </c>
-      <c r="D135" t="b">
-        <v>1</v>
-      </c>
-      <c r="E135" t="s">
-        <v>219</v>
-      </c>
       <c r="H135">
-        <v>14421.4445384545</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+        <v>138093.51284795001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>10.3054375133703</v>
+        <v>14.9754176217679</v>
       </c>
       <c r="B136" t="s">
-        <v>220</v>
+        <v>34</v>
       </c>
       <c r="C136">
-        <v>76.735692309060099</v>
+        <v>80.284140464311506</v>
       </c>
       <c r="D136" t="b">
         <v>1</v>
       </c>
       <c r="E136" t="s">
-        <v>221</v>
+        <v>35</v>
       </c>
       <c r="H136">
-        <v>14414.0117050636</v>
+        <v>300135.233133192</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>13.0849246818774</v>
+        <v>15.013722878434899</v>
       </c>
       <c r="B137" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="C137">
-        <v>71.734568638020804</v>
+        <v>91.142814938348494</v>
       </c>
       <c r="D137" t="b">
         <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="H137">
-        <v>14392.5772729491</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+        <v>669644.77691929298</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>16.1242987985467</v>
+        <v>15.023316619352199</v>
       </c>
       <c r="B138" t="s">
-        <v>222</v>
+        <v>70</v>
       </c>
       <c r="C138">
-        <v>73.819213151102701</v>
+        <v>75.208481137986496</v>
       </c>
       <c r="D138" t="b">
         <v>1</v>
       </c>
       <c r="E138" t="s">
-        <v>223</v>
+        <v>71</v>
       </c>
       <c r="H138">
-        <v>13335.6504350133</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+        <v>96484.136351083303</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>4.6303679995145002</v>
+        <v>15.0331980344321</v>
       </c>
       <c r="B139" t="s">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="C139">
-        <v>90.668534998273699</v>
+        <v>78.437749742771302</v>
       </c>
       <c r="D139" t="b">
         <v>1</v>
       </c>
       <c r="E139" t="s">
-        <v>225</v>
+        <v>41</v>
       </c>
       <c r="H139">
-        <v>13068.351013822299</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+        <v>170728.07827035</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>10.550922874941</v>
+        <v>15.055553004168001</v>
       </c>
       <c r="B140" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C140">
-        <v>73.232393611137397</v>
+        <v>76.950081074977106</v>
       </c>
       <c r="D140" t="b">
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>27</v>
+        <v>241</v>
       </c>
       <c r="H140">
-        <v>12928.8274289602</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+        <v>12007.948117056399</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>8.0902103547575699</v>
+        <v>15.275822506154</v>
       </c>
       <c r="B141" t="s">
-        <v>227</v>
+        <v>62</v>
       </c>
       <c r="C141">
-        <v>71.206484441236398</v>
+        <v>71.400213315774195</v>
       </c>
       <c r="D141" t="b">
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>228</v>
+        <v>63</v>
       </c>
       <c r="H141">
-        <v>12735.7141970995</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+        <v>101187.506676693</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>10.834851823410499</v>
+        <v>15.3634436799921</v>
       </c>
       <c r="B142" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="C142">
-        <v>85.441410192425593</v>
+        <v>71.579564266446894</v>
       </c>
       <c r="D142" t="b">
         <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H142">
-        <v>12666.052171236401</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7231.4634897504802</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>9.7067951640661398</v>
+        <v>15.4489711803147</v>
       </c>
       <c r="B143" t="s">
-        <v>231</v>
+        <v>293</v>
       </c>
       <c r="C143">
-        <v>75.957082353015494</v>
+        <v>77.985596061973496</v>
       </c>
       <c r="D143" t="b">
         <v>1</v>
       </c>
       <c r="E143" t="s">
-        <v>232</v>
+        <v>294</v>
       </c>
       <c r="H143">
-        <v>12596.938931062001</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3413.4542240494802</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>10.0214933680175</v>
+        <v>15.4950021621631</v>
       </c>
       <c r="B144" t="s">
-        <v>59</v>
+        <v>268</v>
       </c>
       <c r="C144">
-        <v>70.531031531459803</v>
+        <v>74.101145416953102</v>
       </c>
       <c r="D144" t="b">
         <v>1</v>
       </c>
       <c r="E144" t="s">
-        <v>60</v>
+        <v>269</v>
       </c>
       <c r="H144">
-        <v>12397.698391735101</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8340.5641601559491</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>22.306283069616899</v>
+        <v>15.5149873086313</v>
       </c>
       <c r="B145" t="s">
-        <v>233</v>
+        <v>87</v>
       </c>
       <c r="C145">
-        <v>77.477687882478605</v>
+        <v>80.883088804377806</v>
       </c>
       <c r="D145" t="b">
         <v>1</v>
       </c>
       <c r="E145" t="s">
-        <v>234</v>
+        <v>88</v>
       </c>
       <c r="H145">
-        <v>12354.8739780657</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+        <v>68766.030900024096</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>17.646850969481601</v>
+        <v>15.7580494541328</v>
       </c>
       <c r="B146" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="C146">
-        <v>75.830613054890193</v>
+        <v>75.796188841251706</v>
       </c>
       <c r="D146" t="b">
         <v>1</v>
       </c>
       <c r="E146" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="H146">
-        <v>12313.302517874999</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9085.3678463820597</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>8.7192180620694995</v>
+        <v>15.854133476513899</v>
       </c>
       <c r="B147" t="s">
-        <v>237</v>
+        <v>170</v>
       </c>
       <c r="C147">
-        <v>71.977846627690496</v>
+        <v>79.035805620921295</v>
       </c>
       <c r="D147" t="b">
         <v>1</v>
       </c>
       <c r="E147" t="s">
-        <v>101</v>
+        <v>171</v>
       </c>
       <c r="H147">
-        <v>12167.1087078085</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+        <v>22890.150485006001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>9.9443386253772097</v>
+        <v>15.868609003038699</v>
       </c>
       <c r="B148" t="s">
-        <v>238</v>
+        <v>74</v>
       </c>
       <c r="C148">
-        <v>77.272129673343898</v>
+        <v>91.414540832921304</v>
       </c>
       <c r="D148" t="b">
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>239</v>
+        <v>75</v>
       </c>
       <c r="H148">
-        <v>12119.1349764143</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+        <v>90232.208630877096</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>9.4291130944598098</v>
+        <v>15.878453999887</v>
       </c>
       <c r="B149" t="s">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="C149">
-        <v>86.014840970781606</v>
+        <v>74.338510383767002</v>
       </c>
       <c r="D149" t="b">
         <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="H149">
-        <v>12064.442529514001</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+        <v>19785.735425794701</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>15.055553004168001</v>
+        <v>15.894453869287201</v>
       </c>
       <c r="B150" t="s">
-        <v>241</v>
+        <v>133</v>
       </c>
       <c r="C150">
-        <v>76.950081074977106</v>
+        <v>84.554816095486302</v>
       </c>
       <c r="D150" t="b">
         <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="H150">
-        <v>12007.948117056399</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+        <v>34293.063933993697</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>14.337633153981299</v>
+        <v>15.9661127816329</v>
       </c>
       <c r="B151" t="s">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="C151">
-        <v>72.6758392490039</v>
+        <v>88.096891959837095</v>
       </c>
       <c r="D151" t="b">
         <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="H151">
-        <v>11894.2926352226</v>
+        <v>78311.543039553304</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>14.1666048515771</v>
+        <v>15.972004765723501</v>
       </c>
       <c r="B152" t="s">
-        <v>245</v>
+        <v>37</v>
       </c>
       <c r="C152">
-        <v>71.444776516372301</v>
+        <v>85.0428570686272</v>
       </c>
       <c r="D152" t="b">
         <v>1</v>
       </c>
       <c r="E152" t="s">
-        <v>246</v>
+        <v>38</v>
       </c>
       <c r="H152">
-        <v>11871.782200788601</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+        <v>217022.545470301</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>24.5012531647461</v>
+        <v>16.008032273605</v>
       </c>
       <c r="B153" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="C153">
-        <v>73.140480961173793</v>
+        <v>79.973340429772506</v>
       </c>
       <c r="D153" t="b">
         <v>1</v>
       </c>
       <c r="E153" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H153">
-        <v>11859.7164547132</v>
+        <v>4382.9535390660903</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>8.5076529020684308</v>
+        <v>16.063060793866899</v>
       </c>
       <c r="B154" t="s">
-        <v>249</v>
+        <v>44</v>
       </c>
       <c r="C154">
-        <v>83.412415980722798</v>
+        <v>86.677885808107007</v>
       </c>
       <c r="D154" t="b">
         <v>1</v>
       </c>
       <c r="E154" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H154">
-        <v>11680.5326550917</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+        <v>154111.29887535999</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>27.478725172400001</v>
+        <v>16.1080021087195</v>
       </c>
       <c r="B155" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="C155">
-        <v>71.322250656912004</v>
+        <v>76.120558884048805</v>
       </c>
       <c r="D155" t="b">
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="H155">
-        <v>11503.3210169373</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+        <v>14591.932970681401</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>22.395553346362199</v>
+        <v>16.1242987985467</v>
       </c>
       <c r="B156" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="C156">
-        <v>71.251345445126901</v>
+        <v>73.819213151102701</v>
       </c>
       <c r="D156" t="b">
         <v>1</v>
       </c>
       <c r="E156" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="H156">
-        <v>11316.5424388093</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+        <v>13335.6504350133</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>8.7023530074474902</v>
+        <v>16.141199438623801</v>
       </c>
       <c r="B157" t="s">
-        <v>254</v>
+        <v>148</v>
       </c>
       <c r="C157">
-        <v>81.556880977644298</v>
+        <v>77.845093530776893</v>
       </c>
       <c r="D157" t="b">
         <v>1</v>
       </c>
       <c r="E157" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="H157">
-        <v>11140.6111035709</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+        <v>28723.119222507899</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>18.703178277947298</v>
+        <v>16.2359528209081</v>
       </c>
       <c r="B158" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="C158">
-        <v>81.270160587714201</v>
+        <v>81.775685297943994</v>
       </c>
       <c r="D158" t="b">
         <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="H158">
-        <v>10948.6754408046</v>
+        <v>4910.7754257483602</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>13.9723662292801</v>
+        <v>16.353955469231298</v>
       </c>
       <c r="B159" t="s">
-        <v>257</v>
+        <v>32</v>
       </c>
       <c r="C159">
-        <v>72.049841730564495</v>
+        <v>94.918703250514994</v>
       </c>
       <c r="D159" t="b">
         <v>1</v>
       </c>
       <c r="E159" t="s">
-        <v>258</v>
+        <v>33</v>
       </c>
       <c r="H159">
-        <v>10899.2449939985</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+        <v>302072.55660798098</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>13.972604279494499</v>
+        <v>16.683752535158199</v>
       </c>
       <c r="B160" t="s">
-        <v>259</v>
+        <v>126</v>
       </c>
       <c r="C160">
-        <v>75.120703068220607</v>
+        <v>70.836745584762397</v>
       </c>
       <c r="D160" t="b">
         <v>1</v>
       </c>
       <c r="E160" t="s">
-        <v>260</v>
+        <v>45</v>
       </c>
       <c r="H160">
-        <v>10899.2449939985</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+        <v>38210.3593421279</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>8.4699573179389596</v>
+        <v>16.971534752194898</v>
       </c>
       <c r="B161" t="s">
-        <v>261</v>
+        <v>60</v>
       </c>
       <c r="C161">
-        <v>83.286563397288703</v>
+        <v>77.178424003430607</v>
       </c>
       <c r="D161" t="b">
         <v>1</v>
       </c>
       <c r="E161" t="s">
-        <v>262</v>
+        <v>61</v>
       </c>
       <c r="H161">
-        <v>10799.7242203356</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+        <v>103292.48215387001</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>13.596801003430601</v>
+        <v>17.0460603414075</v>
       </c>
       <c r="B162" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="C162">
-        <v>71.476885195867396</v>
+        <v>72.846970594556893</v>
       </c>
       <c r="D162" t="b">
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="H162">
-        <v>10606.7626845594</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+        <v>21834.2032741107</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>11.182923101015399</v>
+        <v>17.119869910738501</v>
       </c>
       <c r="B163" t="s">
-        <v>263</v>
+        <v>139</v>
       </c>
       <c r="C163">
-        <v>78.130737965002297</v>
+        <v>72.734854128060107</v>
       </c>
       <c r="D163" t="b">
         <v>1</v>
       </c>
       <c r="E163" t="s">
-        <v>264</v>
+        <v>140</v>
       </c>
       <c r="H163">
-        <v>10025.617369359499</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+        <v>30457.432673862699</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>8.7685238640945702</v>
+        <v>17.217928040709001</v>
       </c>
       <c r="B164" t="s">
-        <v>265</v>
+        <v>137</v>
       </c>
       <c r="C164">
-        <v>74.070729887399693</v>
+        <v>88.650117466340205</v>
       </c>
       <c r="D164" t="b">
         <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="H164">
-        <v>9890.1940928241693</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+        <v>20459.410012548698</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>15.7580494541328</v>
+        <v>17.3162541126948</v>
       </c>
       <c r="B165" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="C165">
-        <v>75.796188841251706</v>
+        <v>70.932517820092698</v>
       </c>
       <c r="D165" t="b">
         <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="H165">
-        <v>9085.3678463820597</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4368.6792897749601</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>13.4724678053161</v>
+        <v>17.379330463588399</v>
       </c>
       <c r="B166" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C166">
-        <v>70.004039378106796</v>
+        <v>71.851648819238207</v>
       </c>
       <c r="D166" t="b">
         <v>1</v>
       </c>
       <c r="E166" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="H166">
-        <v>8694.6170693972399</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+        <v>32943.578547569603</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>15.4950021621631</v>
+        <v>17.460976987465401</v>
       </c>
       <c r="B167" t="s">
-        <v>269</v>
+        <v>127</v>
       </c>
       <c r="C167">
-        <v>74.101145416953102</v>
+        <v>73.053474095102899</v>
       </c>
       <c r="D167" t="b">
         <v>1</v>
       </c>
       <c r="E167" t="s">
-        <v>270</v>
+        <v>51</v>
       </c>
       <c r="H167">
-        <v>8340.5641601559491</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+        <v>36668.180313255201</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>20.492651325465999</v>
+        <v>17.509958413433601</v>
       </c>
       <c r="B168" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="C168">
-        <v>74.054479919059602</v>
+        <v>79.227968777130698</v>
       </c>
       <c r="D168" t="b">
         <v>1</v>
       </c>
       <c r="E168" t="s">
-        <v>272</v>
+        <v>138</v>
       </c>
       <c r="H168">
-        <v>8077.3470785643804</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+        <v>18789.2614993641</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>26.4944756305526</v>
+        <v>17.572997416703501</v>
       </c>
       <c r="B169" t="s">
-        <v>273</v>
+        <v>137</v>
       </c>
       <c r="C169">
-        <v>71.134471476233998</v>
+        <v>81.0582416444757</v>
       </c>
       <c r="D169" t="b">
         <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>274</v>
+        <v>138</v>
       </c>
       <c r="H169">
-        <v>7861.1498279342504</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+        <v>25231.3539607046</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>8.1536350298989095</v>
+        <v>17.646850969481601</v>
       </c>
       <c r="B170" t="s">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="C170">
-        <v>78.382285295409105</v>
+        <v>75.830613054890193</v>
       </c>
       <c r="D170" t="b">
         <v>1</v>
       </c>
       <c r="E170" t="s">
-        <v>157</v>
+        <v>235</v>
       </c>
       <c r="H170">
-        <v>7579.79267203581</v>
+        <v>12313.302517874999</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>15.3634436799921</v>
+        <v>18.0140340784221</v>
       </c>
       <c r="B171" t="s">
-        <v>216</v>
+        <v>50</v>
       </c>
       <c r="C171">
-        <v>71.579564266446894</v>
+        <v>88.848454990420706</v>
       </c>
       <c r="D171" t="b">
         <v>1</v>
       </c>
       <c r="E171" t="s">
-        <v>217</v>
+        <v>51</v>
       </c>
       <c r="H171">
-        <v>7231.4634897504802</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+        <v>120310.65743459899</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
+        <v>18.187472053170001</v>
+      </c>
+      <c r="B172" t="s">
+        <v>135</v>
+      </c>
+      <c r="C172">
+        <v>80.665879896190503</v>
+      </c>
+      <c r="D172" t="b">
+        <v>1</v>
+      </c>
+      <c r="E172" t="s">
+        <v>136</v>
+      </c>
+      <c r="H172">
+        <v>33774.877500791401</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>18.389159236756001</v>
+      </c>
+      <c r="B173" t="s">
+        <v>195</v>
+      </c>
+      <c r="C173">
+        <v>76.477574428347594</v>
+      </c>
+      <c r="D173" t="b">
+        <v>1</v>
+      </c>
+      <c r="E173" t="s">
+        <v>61</v>
+      </c>
+      <c r="H173">
+        <v>16949.220953733598</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>18.557818392862998</v>
+      </c>
+      <c r="B174" t="s">
+        <v>111</v>
+      </c>
+      <c r="C174">
+        <v>91.4008299054465</v>
+      </c>
+      <c r="D174" t="b">
+        <v>1</v>
+      </c>
+      <c r="E174" t="s">
+        <v>112</v>
+      </c>
+      <c r="H174">
+        <v>48825.957611390302</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>18.703178277947298</v>
+      </c>
+      <c r="B175" t="s">
+        <v>254</v>
+      </c>
+      <c r="C175">
+        <v>81.270160587714201</v>
+      </c>
+      <c r="D175" t="b">
+        <v>1</v>
+      </c>
+      <c r="E175" t="s">
+        <v>255</v>
+      </c>
+      <c r="H175">
+        <v>10948.6754408046</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>18.790684130648501</v>
+      </c>
+      <c r="B176" t="s">
+        <v>117</v>
+      </c>
+      <c r="C176">
+        <v>70.047855590456095</v>
+      </c>
+      <c r="D176" t="b">
+        <v>1</v>
+      </c>
+      <c r="E176" t="s">
+        <v>118</v>
+      </c>
+      <c r="H176">
+        <v>47783.047712384403</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>19.012478506301299</v>
+      </c>
+      <c r="B177" t="s">
+        <v>254</v>
+      </c>
+      <c r="C177">
+        <v>82.229300427187894</v>
+      </c>
+      <c r="D177" t="b">
+        <v>1</v>
+      </c>
+      <c r="E177" t="s">
+        <v>255</v>
+      </c>
+      <c r="H177">
+        <v>3860.8044378479599</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>19.039036337118599</v>
+      </c>
+      <c r="B178" t="s">
+        <v>143</v>
+      </c>
+      <c r="C178">
+        <v>75.551320034241598</v>
+      </c>
+      <c r="D178" t="b">
+        <v>1</v>
+      </c>
+      <c r="E178" t="s">
+        <v>144</v>
+      </c>
+      <c r="H178">
+        <v>29744.822501987899</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>19.1455072754427</v>
+      </c>
+      <c r="B179" t="s">
+        <v>189</v>
+      </c>
+      <c r="C179">
+        <v>72.808943869243194</v>
+      </c>
+      <c r="D179" t="b">
+        <v>1</v>
+      </c>
+      <c r="E179" t="s">
+        <v>190</v>
+      </c>
+      <c r="H179">
+        <v>18051.7034934365</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A180">
         <v>19.219618225602598</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B180" t="s">
+        <v>275</v>
+      </c>
+      <c r="C180">
+        <v>81.914207468517404</v>
+      </c>
+      <c r="D180" t="b">
+        <v>1</v>
+      </c>
+      <c r="E180" t="s">
         <v>276</v>
       </c>
-      <c r="C172">
-        <v>81.914207468517404</v>
-      </c>
-      <c r="D172" t="b">
-        <v>1</v>
-      </c>
-      <c r="E172" t="s">
-        <v>277</v>
-      </c>
-      <c r="H172">
+      <c r="H180">
         <v>7214.8745626897899</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A173">
-        <v>7.4990067141985497</v>
-      </c>
-      <c r="B173" t="s">
-        <v>278</v>
-      </c>
-      <c r="C173">
-        <v>75.545009979857596</v>
-      </c>
-      <c r="D173" t="b">
-        <v>1</v>
-      </c>
-      <c r="E173" t="s">
-        <v>101</v>
-      </c>
-      <c r="H173">
-        <v>7103.02467172242</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A174">
-        <v>10.2103804193997</v>
-      </c>
-      <c r="B174" t="s">
-        <v>279</v>
-      </c>
-      <c r="C174">
-        <v>76.447277261543107</v>
-      </c>
-      <c r="D174" t="b">
-        <v>1</v>
-      </c>
-      <c r="E174" t="s">
-        <v>280</v>
-      </c>
-      <c r="H174">
-        <v>6958.0602113640098</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A175">
-        <v>6.0318943995866903</v>
-      </c>
-      <c r="B175" t="s">
-        <v>281</v>
-      </c>
-      <c r="C175">
-        <v>78.9136734098918</v>
-      </c>
-      <c r="D175" t="b">
-        <v>1</v>
-      </c>
-      <c r="E175" t="s">
-        <v>282</v>
-      </c>
-      <c r="H175">
-        <v>6620.7053621443301</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A176">
-        <v>8.8509708477544091</v>
-      </c>
-      <c r="B176" t="s">
-        <v>283</v>
-      </c>
-      <c r="C176">
-        <v>78.457522699800506</v>
-      </c>
-      <c r="D176" t="b">
-        <v>1</v>
-      </c>
-      <c r="E176" t="s">
-        <v>12</v>
-      </c>
-      <c r="H176">
-        <v>6333.6362592958603</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A177">
-        <v>8.9447590733776998</v>
-      </c>
-      <c r="B177" t="s">
-        <v>284</v>
-      </c>
-      <c r="C177">
-        <v>74.649849208976207</v>
-      </c>
-      <c r="D177" t="b">
-        <v>1</v>
-      </c>
-      <c r="E177" t="s">
-        <v>285</v>
-      </c>
-      <c r="H177">
-        <v>5839.4953735645004</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A178">
-        <v>16.2359528209081</v>
-      </c>
-      <c r="B178" t="s">
-        <v>222</v>
-      </c>
-      <c r="C178">
-        <v>81.775685297943994</v>
-      </c>
-      <c r="D178" t="b">
-        <v>1</v>
-      </c>
-      <c r="E178" t="s">
-        <v>223</v>
-      </c>
-      <c r="H178">
-        <v>4910.7754257483602</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A179">
-        <v>7.3386309821888904</v>
-      </c>
-      <c r="B179" t="s">
-        <v>95</v>
-      </c>
-      <c r="C179">
-        <v>70.365115244838407</v>
-      </c>
-      <c r="D179" t="b">
-        <v>1</v>
-      </c>
-      <c r="E179" t="s">
-        <v>21</v>
-      </c>
-      <c r="H179">
-        <v>4457.1163890152002</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A180">
-        <v>16.008032273605</v>
-      </c>
-      <c r="B180" t="s">
-        <v>286</v>
-      </c>
-      <c r="C180">
-        <v>79.973340429772506</v>
-      </c>
-      <c r="D180" t="b">
-        <v>1</v>
-      </c>
-      <c r="E180" t="s">
-        <v>287</v>
-      </c>
-      <c r="H180">
-        <v>4382.9535390660903</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
-        <v>17.3162541126948</v>
+        <v>19.987100844344901</v>
       </c>
       <c r="B181" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="C181">
-        <v>70.932517820092698</v>
+        <v>76.555512764520998</v>
       </c>
       <c r="D181" t="b">
         <v>1</v>
       </c>
       <c r="E181" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="H181">
-        <v>4368.6792897749601</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+        <v>2466.48553472187</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
-        <v>11.7641824126081</v>
+        <v>20.286675565976999</v>
       </c>
       <c r="B182" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="C182">
-        <v>80.510321917445395</v>
+        <v>87.718245578739001</v>
       </c>
       <c r="D182" t="b">
         <v>1</v>
       </c>
       <c r="E182" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H182">
-        <v>4215.8835830804201</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+        <v>79197.504832926104</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
-        <v>7.3566008039928104</v>
+        <v>20.492651325465999</v>
       </c>
       <c r="B183" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="C183">
-        <v>87.880473533074706</v>
+        <v>74.054479919059602</v>
       </c>
       <c r="D183" t="b">
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>178</v>
+        <v>271</v>
       </c>
       <c r="H183">
-        <v>4085.9812283676001</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8077.3470785643804</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
-        <v>19.012478506301299</v>
+        <v>20.6217099453293</v>
       </c>
       <c r="B184" t="s">
-        <v>255</v>
+        <v>107</v>
       </c>
       <c r="C184">
-        <v>82.229300427187894</v>
+        <v>92.165932300632207</v>
       </c>
       <c r="D184" t="b">
         <v>1</v>
       </c>
       <c r="E184" t="s">
-        <v>256</v>
+        <v>108</v>
       </c>
       <c r="H184">
-        <v>3860.8044378479599</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+        <v>52295.123441220399</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
-        <v>10.6234630464558</v>
+        <v>22.306283069616899</v>
       </c>
       <c r="B185" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="C185">
-        <v>73.221934745095496</v>
+        <v>77.477687882478605</v>
       </c>
       <c r="D185" t="b">
         <v>1</v>
       </c>
       <c r="E185" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="H185">
-        <v>3853.8320637223801</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+        <v>12354.8739780657</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
-        <v>12.7024210276931</v>
+        <v>22.332339885791001</v>
       </c>
       <c r="B186" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C186">
-        <v>71.437966117276005</v>
+        <v>76.466868090728198</v>
       </c>
       <c r="D186" t="b">
         <v>1</v>
       </c>
       <c r="E186" t="s">
-        <v>52</v>
+        <v>300</v>
       </c>
       <c r="H186">
-        <v>3639.1609586670502</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+        <v>2838.4844471817401</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
-        <v>4.2110670063696096</v>
+        <v>22.395553346362199</v>
       </c>
       <c r="B187" t="s">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="C187">
-        <v>77.079469975011193</v>
+        <v>71.251345445126901</v>
       </c>
       <c r="D187" t="b">
         <v>1</v>
       </c>
       <c r="E187" t="s">
-        <v>293</v>
+        <v>252</v>
       </c>
       <c r="H187">
-        <v>3496.0919390127701</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+        <v>11316.5424388093</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
-        <v>15.4489711803147</v>
+        <v>22.802954475199599</v>
       </c>
       <c r="B188" t="s">
-        <v>294</v>
+        <v>213</v>
       </c>
       <c r="C188">
-        <v>77.985596061973496</v>
+        <v>79.813639162276303</v>
       </c>
       <c r="D188" t="b">
         <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>295</v>
+        <v>214</v>
       </c>
       <c r="H188">
-        <v>3413.4542240494802</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+        <v>14686.690376365401</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
-        <v>8.6078902080839903</v>
+        <v>23.653009082440899</v>
       </c>
       <c r="B189" t="s">
-        <v>159</v>
+        <v>76</v>
       </c>
       <c r="C189">
-        <v>78.216643199743999</v>
+        <v>78.224165339802198</v>
       </c>
       <c r="D189" t="b">
         <v>1</v>
       </c>
       <c r="E189" t="s">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="H189">
-        <v>3375.5886871338698</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+        <v>79823.199970504793</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>23.6782184406403</v>
       </c>
       <c r="B190" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C190">
         <v>80.895151753186099</v>
@@ -5630,110 +5734,110 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H190">
         <v>3253.0174042528201</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
-        <v>9.2801652831168493</v>
+        <v>24.5012531647461</v>
       </c>
       <c r="B191" t="s">
-        <v>298</v>
+        <v>246</v>
       </c>
       <c r="C191">
-        <v>70.322877166563998</v>
+        <v>73.140480961173793</v>
       </c>
       <c r="D191" t="b">
         <v>1</v>
       </c>
       <c r="E191" t="s">
-        <v>299</v>
+        <v>247</v>
       </c>
       <c r="H191">
-        <v>3117.0511835720099</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+        <v>11859.7164547132</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
-        <v>22.332339885791001</v>
+        <v>26.4944756305526</v>
       </c>
       <c r="B192" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="C192">
-        <v>76.466868090728198</v>
+        <v>71.134471476233998</v>
       </c>
       <c r="D192" t="b">
         <v>1</v>
       </c>
       <c r="E192" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="H192">
-        <v>2838.4844471817401</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7861.1498279342504</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
-        <v>19.987100844344901</v>
+        <v>26.849380013378202</v>
       </c>
       <c r="B193" t="s">
-        <v>302</v>
+        <v>182</v>
       </c>
       <c r="C193">
-        <v>76.555512764520998</v>
+        <v>70.378187236064804</v>
       </c>
       <c r="D193" t="b">
         <v>1</v>
       </c>
       <c r="E193" t="s">
+        <v>183</v>
+      </c>
+      <c r="H193">
+        <v>18820.969408996702</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>27.478725172400001</v>
+      </c>
+      <c r="B194" t="s">
+        <v>249</v>
+      </c>
+      <c r="C194">
+        <v>71.322250656912004</v>
+      </c>
+      <c r="D194" t="b">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>250</v>
+      </c>
+      <c r="H194">
+        <v>11503.3210169373</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>33.450761383051898</v>
+      </c>
+      <c r="B195" t="s">
         <v>303</v>
       </c>
-      <c r="H193">
-        <v>2466.48553472187</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A194">
-        <v>33.450761383051898</v>
-      </c>
-      <c r="B194" t="s">
+      <c r="C195">
+        <v>73.076063187723406</v>
+      </c>
+      <c r="D195" t="b">
+        <v>1</v>
+      </c>
+      <c r="E195" t="s">
         <v>304</v>
       </c>
-      <c r="C194">
-        <v>73.076063187723406</v>
-      </c>
-      <c r="D194" t="b">
-        <v>1</v>
-      </c>
-      <c r="E194" t="s">
-        <v>305</v>
-      </c>
-      <c r="H194">
+      <c r="H195">
         <v>2045.3459649123099</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A195">
-        <v>9.7931123720845008</v>
-      </c>
-      <c r="B195" t="s">
-        <v>263</v>
-      </c>
-      <c r="C195">
-        <v>74.200006869549895</v>
-      </c>
-      <c r="D195" t="b">
-        <v>1</v>
-      </c>
-      <c r="E195" t="s">
-        <v>264</v>
-      </c>
-      <c r="H195">
-        <v>1147.4035733337801</v>
       </c>
     </row>
   </sheetData>

--- a/gc-ms results/260930 raw oil.xlsx
+++ b/gc-ms results/260930 raw oil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\Notes\gc-ms results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BFC335-ADF9-4868-B7AF-509B182ACF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AA31C6-F7AD-4A96-9545-E1877E125357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9DDEE15F-E737-4B6C-AA01-47268D57280C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="312">
   <si>
     <t>Component RT</t>
   </si>
@@ -966,12 +966,18 @@
   </si>
   <si>
     <t>carboxylic acid</t>
+  </si>
+  <si>
+    <t>Column1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1108,7 +1114,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1288,8 +1294,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1404,6 +1416,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1449,8 +1498,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1510,8 +1566,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{02696040-A310-4945-97A4-2FB32B401A3D}" name="Table1" displayName="Table1" ref="A1:H195" totalsRowShown="0">
-  <autoFilter ref="A1:H195" xr:uid="{02696040-A310-4945-97A4-2FB32B401A3D}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{02696040-A310-4945-97A4-2FB32B401A3D}" name="Table1" displayName="Table1" ref="A1:I195" totalsRowShown="0">
+  <autoFilter ref="A1:I195" xr:uid="{02696040-A310-4945-97A4-2FB32B401A3D}">
     <filterColumn colId="2">
       <customFilters>
         <customFilter operator="greaterThan" val="85"/>
@@ -1523,10 +1579,10 @@
       </customFilters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H195">
-    <sortCondition ref="A1:A195"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A22:I171">
+    <sortCondition descending="1" ref="I1:I195"/>
   </sortState>
-  <tableColumns count="8">
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{01AC00D2-410B-4476-B377-1C3B8197E384}" name="Component RT"/>
     <tableColumn id="2" xr3:uid="{1133B22A-391B-4B5C-91B2-6E57F5886970}" name="Compound Name"/>
     <tableColumn id="3" xr3:uid="{E38942FF-10BF-4BBC-8FC3-13FC41C0966F}" name="Match Factor"/>
@@ -1535,6 +1591,7 @@
     <tableColumn id="6" xr3:uid="{18902260-5B9A-48CF-A7D0-647D0203620B}" name="Area %"/>
     <tableColumn id="7" xr3:uid="{4D7F21DC-EE76-40BF-B1F3-C4638D394C59}" name="Area % Max."/>
     <tableColumn id="8" xr3:uid="{5109D0E5-1D89-49C1-83D5-3564056D1BCA}" name="Base Peak Area"/>
+    <tableColumn id="9" xr3:uid="{AAFCF406-DC84-4FEA-93D4-7347C7790AE9}" name="Column1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1857,7 +1914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05663A3C-3C2C-4760-A06E-2E5E378BF6B9}">
-  <dimension ref="A1:N195"/>
+  <dimension ref="A1:O195"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" customWidth="1"/>
@@ -1867,12 +1924,12 @@
     <col min="5" max="5" width="9.77734375" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="12.77734375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" customWidth="1"/>
-    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.44140625" customWidth="1"/>
+    <col min="10" max="10" width="13.109375" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1898,25 +1955,28 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J1" t="s">
         <v>306</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>305</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>307</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>308</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>309</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>3.1799054323826201</v>
       </c>
@@ -1936,7 +1996,7 @@
         <v>29375.767883561799</v>
       </c>
     </row>
-    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>4.2110670063696096</v>
       </c>
@@ -1956,7 +2016,7 @@
         <v>3496.0919390127701</v>
       </c>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4.23448639810759</v>
       </c>
@@ -1976,7 +2036,7 @@
         <v>26789.263654456001</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4.2393737685011903</v>
       </c>
@@ -1996,7 +2056,7 @@
         <v>19150.127014097299</v>
       </c>
     </row>
-    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4.6303679995145002</v>
       </c>
@@ -2016,7 +2076,7 @@
         <v>13068.351013822299</v>
       </c>
     </row>
-    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5.37273448999093</v>
       </c>
@@ -2036,7 +2096,7 @@
         <v>65357.922859203703</v>
       </c>
     </row>
-    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5.3766850903912999</v>
       </c>
@@ -2056,7 +2116,7 @@
         <v>54152.145098895198</v>
       </c>
     </row>
-    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>5.7559266958886504</v>
       </c>
@@ -2076,7 +2136,7 @@
         <v>19988.389436862599</v>
       </c>
     </row>
-    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>6.0113559101513303</v>
       </c>
@@ -2096,7 +2156,7 @@
         <v>97958.357444017107</v>
       </c>
     </row>
-    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>6.0318943995866903</v>
       </c>
@@ -2116,7 +2176,7 @@
         <v>6620.7053621443301</v>
       </c>
     </row>
-    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>6.7367122934712604</v>
       </c>
@@ -2136,7 +2196,7 @@
         <v>57727.953314653198</v>
       </c>
     </row>
-    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>6.7878696891479704</v>
       </c>
@@ -2156,7 +2216,7 @@
         <v>61737.255655543297</v>
       </c>
     </row>
-    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>6.8368060723470601</v>
       </c>
@@ -2176,7 +2236,7 @@
         <v>34740.820103188598</v>
       </c>
     </row>
-    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>7.1541843982103597</v>
       </c>
@@ -2196,7 +2256,7 @@
         <v>14421.4445384545</v>
       </c>
     </row>
-    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>7.3386309821888904</v>
       </c>
@@ -2216,7 +2276,7 @@
         <v>4457.1163890152002</v>
       </c>
     </row>
-    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>7.3566008039928104</v>
       </c>
@@ -2236,7 +2296,7 @@
         <v>4085.9812283676001</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>7.4990067141985497</v>
       </c>
@@ -2256,7 +2316,7 @@
         <v>7103.02467172242</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>7.7565122990738704</v>
       </c>
@@ -2276,7 +2336,7 @@
         <v>23247.744464137599</v>
       </c>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>7.7601624677887102</v>
       </c>
@@ -2296,7 +2356,7 @@
         <v>34902.493095443097</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>7.8295239439419202</v>
       </c>
@@ -2316,7 +2376,7 @@
         <v>18126.656668075299</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>8.0179614989319692</v>
       </c>
@@ -2336,31 +2396,35 @@
         <v>9757329.7736495901</v>
       </c>
       <c r="I22">
-        <f>J22+H59+H159+H152</f>
-        <v>17644008.236138448</v>
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>0.58059514098650855</v>
       </c>
       <c r="J22">
+        <f>K22+H59+H159+H152</f>
+        <v>17668112.437237151</v>
+      </c>
+      <c r="K22">
         <f>H22+H43+H49+H53+H63+H66+H68+H78+H79+H86+H93+H94+H99+H100+H114+H122+H137+H171+H154</f>
-        <v>17019701.733017672</v>
-      </c>
-      <c r="K22">
+        <v>16805737.914152339</v>
+      </c>
+      <c r="L22">
         <f>H53+H79+H88+H94+H99+H114+H152+H154+H171</f>
-        <v>2976273.2351659397</v>
-      </c>
-      <c r="L22">
+        <v>2680913.9398656618</v>
+      </c>
+      <c r="M22">
         <f>H86+H137+H171</f>
-        <v>905078.18882758496</v>
-      </c>
-      <c r="M22">
+        <v>654681.15853099606</v>
+      </c>
+      <c r="N22">
         <f>H86</f>
+        <v>395358.45861314097</v>
+      </c>
+      <c r="O22">
+        <f>H159</f>
         <v>115122.754473693</v>
       </c>
-      <c r="N22">
-        <f>H159</f>
-        <v>302072.55660798098</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>8.0293878053180592</v>
       </c>
@@ -2380,7 +2444,7 @@
         <v>132468.163528509</v>
       </c>
     </row>
-    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>8.0902103547575699</v>
       </c>
@@ -2400,7 +2464,7 @@
         <v>12735.7141970995</v>
       </c>
     </row>
-    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>8.1536350298989095</v>
       </c>
@@ -2420,7 +2484,7 @@
         <v>7579.79267203581</v>
       </c>
     </row>
-    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>8.2692867631624303</v>
       </c>
@@ -2440,7 +2504,7 @@
         <v>17748.361236219898</v>
       </c>
     </row>
-    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>8.3180558545224006</v>
       </c>
@@ -2460,7 +2524,7 @@
         <v>50222.026403992197</v>
       </c>
     </row>
-    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>8.3379370198277201</v>
       </c>
@@ -2480,7 +2544,7 @@
         <v>18155.654191129099</v>
       </c>
     </row>
-    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>8.3880021361406207</v>
       </c>
@@ -2500,7 +2564,7 @@
         <v>15871.347320614001</v>
       </c>
     </row>
-    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>8.4699573179389596</v>
       </c>
@@ -2520,7 +2584,7 @@
         <v>10799.7242203356</v>
       </c>
     </row>
-    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>8.5076529020684308</v>
       </c>
@@ -2540,7 +2604,7 @@
         <v>11680.5326550917</v>
       </c>
     </row>
-    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>8.6078902080839903</v>
       </c>
@@ -2560,7 +2624,7 @@
         <v>3375.5886871338698</v>
       </c>
     </row>
-    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>8.7023530074474902</v>
       </c>
@@ -2580,7 +2644,7 @@
         <v>11140.6111035709</v>
       </c>
     </row>
-    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>8.7192180620694995</v>
       </c>
@@ -2600,7 +2664,7 @@
         <v>12167.1087078085</v>
       </c>
     </row>
-    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>8.7685238640945702</v>
       </c>
@@ -2620,7 +2684,7 @@
         <v>9890.1940928241693</v>
       </c>
     </row>
-    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>8.7916382848967203</v>
       </c>
@@ -2640,7 +2704,7 @@
         <v>60011.050902041803</v>
       </c>
     </row>
-    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>8.8509708477544091</v>
       </c>
@@ -2660,7 +2724,7 @@
         <v>6333.6362592958603</v>
       </c>
     </row>
-    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>8.9447590733776998</v>
       </c>
@@ -2680,7 +2744,7 @@
         <v>5839.4953735645004</v>
       </c>
     </row>
-    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>9.0213104323111608</v>
       </c>
@@ -2700,7 +2764,7 @@
         <v>57811.658699866101</v>
       </c>
     </row>
-    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>9.10757684775594</v>
       </c>
@@ -2720,7 +2784,7 @@
         <v>16343.698791933601</v>
       </c>
     </row>
-    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>9.1089548406179297</v>
       </c>
@@ -2740,7 +2804,7 @@
         <v>27298.4423808584</v>
       </c>
     </row>
-    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>9.1398806832516204</v>
       </c>
@@ -2760,47 +2824,51 @@
         <v>15931.5982336054</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>9.2296862494857805</v>
+        <v>11.4526922770967</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C43">
-        <v>98.629706496315904</v>
+        <v>96.278965728001594</v>
       </c>
       <c r="D43" t="b">
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H43">
-        <v>597066.96980136796</v>
-      </c>
-      <c r="J43">
-        <f>J22/I22</f>
-        <v>0.96461651486638555</v>
+        <v>823778.97337447095</v>
+      </c>
+      <c r="I43">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>4.9017721065419899E-2</v>
       </c>
       <c r="K43">
-        <f>K22/$I$22</f>
-        <v>0.16868464326999907</v>
+        <f>K22/J22</f>
+        <v>0.95119034214049492</v>
       </c>
       <c r="L43">
-        <f t="shared" ref="L43:N43" si="0">L22/$I$22</f>
-        <v>5.1296631508808997E-2</v>
+        <f>L22/$J$22</f>
+        <v>0.15173742805798499</v>
       </c>
       <c r="M43">
-        <f t="shared" si="0"/>
-        <v>6.5247506650953965E-3</v>
+        <f t="shared" ref="M43:O43" si="0">M22/$J$22</f>
+        <v>3.705439168199972E-2</v>
       </c>
       <c r="N43">
         <f t="shared" si="0"/>
-        <v>1.7120404420877346E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>2.2376949434614594E-2</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="0"/>
+        <v>6.5158490972165957E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>9.2801652831168493</v>
       </c>
@@ -2820,7 +2888,7 @@
         <v>3117.0511835720099</v>
       </c>
     </row>
-    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>9.3729764256793597</v>
       </c>
@@ -2840,7 +2908,7 @@
         <v>52862.478468167799</v>
       </c>
     </row>
-    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>9.4291130944598098</v>
       </c>
@@ -2860,7 +2928,7 @@
         <v>12064.442529514001</v>
       </c>
     </row>
-    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>9.4913665705502392</v>
       </c>
@@ -2880,7 +2948,7 @@
         <v>15486.074282969401</v>
       </c>
     </row>
-    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>9.4916059342218109</v>
       </c>
@@ -2900,27 +2968,31 @@
         <v>15486.074282969401</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>9.5564512669485797</v>
+        <v>15.013722878434899</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C49">
-        <v>99.050012820341493</v>
+        <v>91.142814938348494</v>
       </c>
       <c r="D49" t="b">
         <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H49">
-        <v>631962.61451091</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>669644.77691929298</v>
+      </c>
+      <c r="I49">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>3.9846198979181749E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>9.6357255930062404</v>
       </c>
@@ -2940,7 +3012,7 @@
         <v>29104.1738035979</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>9.7067951640661398</v>
       </c>
@@ -2960,7 +3032,7 @@
         <v>12596.938931062001</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>9.7931123720845008</v>
       </c>
@@ -2980,27 +3052,49 @@
         <v>1147.4035733337801</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>9.85294248224589</v>
+        <v>9.5564512669485797</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C53">
-        <v>98.551329906675093</v>
+        <v>99.050012820341493</v>
       </c>
       <c r="D53" t="b">
         <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H53">
-        <v>412496.07847163099</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>631962.61451091</v>
+      </c>
+      <c r="I53">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>3.7603978934999678E-2</v>
+      </c>
+      <c r="J53">
+        <v>17644008.236138448</v>
+      </c>
+      <c r="K53">
+        <v>17019701.733017672</v>
+      </c>
+      <c r="L53">
+        <v>2976273.2351659397</v>
+      </c>
+      <c r="M53">
+        <v>905078.18882758496</v>
+      </c>
+      <c r="N53">
+        <v>115122.754473693</v>
+      </c>
+      <c r="O53">
+        <v>302072.55660798098</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>9.9443386253772097</v>
       </c>
@@ -3020,7 +3114,7 @@
         <v>12119.1349764143</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>9.9521455316233602</v>
       </c>
@@ -3040,7 +3134,7 @@
         <v>25389.853421383501</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>10.0214933680175</v>
       </c>
@@ -3060,7 +3154,7 @@
         <v>12397.698391735101</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>10.06747797635</v>
       </c>
@@ -3080,7 +3174,7 @@
         <v>25138.6521230037</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>10.114618364801</v>
       </c>
@@ -3100,27 +3194,46 @@
         <v>76228.153793290199</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>10.181545204642701</v>
+        <v>13.720375473353201</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="C59">
-        <v>94.500177342310394</v>
+        <v>96.322585730815803</v>
       </c>
       <c r="D59" t="b">
         <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="H59">
-        <v>105211.401042495</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>605178.32783679396</v>
+      </c>
+      <c r="I59">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>3.6010220493035601E-2</v>
+      </c>
+      <c r="K59">
+        <v>0.96461651486638555</v>
+      </c>
+      <c r="L59">
+        <v>0.16868464326999907</v>
+      </c>
+      <c r="M59">
+        <v>5.1296631508808997E-2</v>
+      </c>
+      <c r="N59">
+        <v>6.5247506650953965E-3</v>
+      </c>
+      <c r="O59">
+        <v>1.7120404420877346E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>10.2103804193997</v>
       </c>
@@ -3140,7 +3253,7 @@
         <v>6958.0602113640098</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>10.3054375133703</v>
       </c>
@@ -3160,7 +3273,7 @@
         <v>14414.0117050636</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>10.550922874941</v>
       </c>
@@ -3180,27 +3293,31 @@
         <v>12928.8274289602</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>10.563042202035501</v>
+        <v>9.2296862494857805</v>
       </c>
       <c r="B63" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C63">
-        <v>97.589159336245203</v>
+        <v>98.629706496315904</v>
       </c>
       <c r="D63" t="b">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H63">
-        <v>187550.071788587</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>597066.96980136796</v>
+      </c>
+      <c r="I63">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>3.5527566409242275E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>10.580032690739801</v>
       </c>
@@ -3220,7 +3337,7 @@
         <v>16722.670614422401</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>10.6234630464558</v>
       </c>
@@ -3240,27 +3357,31 @@
         <v>3853.8320637223801</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>10.7284068068968</v>
+        <v>12.728796606709</v>
       </c>
       <c r="B66" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C66">
-        <v>98.229805038712101</v>
+        <v>95.808001683239695</v>
       </c>
       <c r="D66" t="b">
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H66">
-        <v>383968.05209737399</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>551212.03965080401</v>
+      </c>
+      <c r="I66">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>3.2799038189606715E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>10.834851823410499</v>
       </c>
@@ -3280,27 +3401,31 @@
         <v>12666.052171236401</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>10.9970390679324</v>
+        <v>14.082482111214899</v>
       </c>
       <c r="B68" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C68">
-        <v>89.423779677660306</v>
+        <v>88.051553401317094</v>
       </c>
       <c r="D68" t="b">
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H68">
-        <v>394381.45044526801</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>501986.68949736102</v>
+      </c>
+      <c r="I68">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>2.9869958228649469E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>11.0312295281733</v>
       </c>
@@ -3320,7 +3445,7 @@
         <v>110508.213682555</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>11.0631142958211</v>
       </c>
@@ -3340,7 +3465,7 @@
         <v>24401.593574081398</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>11.182923101015399</v>
       </c>
@@ -3360,7 +3485,7 @@
         <v>10025.617369359499</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>11.191947982836901</v>
       </c>
@@ -3380,7 +3505,7 @@
         <v>29916.7316171366</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>11.191947982836901</v>
       </c>
@@ -3400,7 +3525,7 @@
         <v>29916.7316171366</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>11.256866590795299</v>
       </c>
@@ -3419,8 +3544,23 @@
       <c r="H74">
         <v>49669.1240596219</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K74">
+        <v>0.96461651486638555</v>
+      </c>
+      <c r="L74">
+        <v>0.16868464326999907</v>
+      </c>
+      <c r="M74">
+        <v>5.1296631508808997E-2</v>
+      </c>
+      <c r="N74">
+        <v>6.5247506650953965E-3</v>
+      </c>
+      <c r="O74">
+        <v>1.7120404420877346E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>11.3249865513181</v>
       </c>
@@ -3440,7 +3580,7 @@
         <v>51640.170860000697</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>11.398311448804</v>
       </c>
@@ -3460,7 +3600,7 @@
         <v>71127.147259326899</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>11.410406702392301</v>
       </c>
@@ -3480,47 +3620,87 @@
         <v>34499.1473809003</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78">
+        <v>12.084716107508299</v>
+      </c>
+      <c r="B78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78">
+        <v>94.960123063347496</v>
+      </c>
+      <c r="D78" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
+        <v>24</v>
+      </c>
+      <c r="H78">
+        <v>418485.651543974</v>
+      </c>
+      <c r="I78">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>2.4901355339568967E-2</v>
+      </c>
+      <c r="K78" s="5">
+        <v>8.0179614989319692</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M78" s="1">
+        <v>58.059514098650858</v>
+      </c>
+      <c r="N78" s="2">
+        <v>0.58059514098650855</v>
+      </c>
+      <c r="O78">
+        <f>N78*100</f>
+        <v>58.059514098650858</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>9.85294248224589</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79">
+        <v>98.551329906675093</v>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" t="s">
+        <v>26</v>
+      </c>
+      <c r="H79">
+        <v>412496.07847163099</v>
+      </c>
+      <c r="I79">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>2.454495485879632E-2</v>
+      </c>
+      <c r="K79" s="6">
         <v>11.4526922770967</v>
       </c>
-      <c r="B78" t="s">
+      <c r="L79" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C78">
-        <v>96.278965728001594</v>
-      </c>
-      <c r="D78" t="b">
-        <v>1</v>
-      </c>
-      <c r="E78" t="s">
-        <v>11</v>
-      </c>
-      <c r="H78">
-        <v>823778.97337447095</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>11.465407386451799</v>
-      </c>
-      <c r="B79" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79">
-        <v>90.207956351643304</v>
-      </c>
-      <c r="D79" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" t="s">
-        <v>22</v>
-      </c>
-      <c r="H79">
-        <v>355383.19510815298</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="M79" s="3">
+        <v>4.9017721065419897</v>
+      </c>
+      <c r="N79" s="4">
+        <v>4.9017721065419899E-2</v>
+      </c>
+      <c r="O79">
+        <f t="shared" ref="O79:O122" si="1">N79*100</f>
+        <v>4.9017721065419897</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>11.6172161467303</v>
       </c>
@@ -3539,8 +3719,25 @@
       <c r="H80">
         <v>62310.480085619398</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K80" s="5">
+        <v>9.5564512669485797</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M80" s="2">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <f t="shared" ref="M79:N136" si="2">M80*100</f>
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>11.706060929721801</v>
       </c>
@@ -3559,8 +3756,25 @@
       <c r="H81">
         <v>23534.456924034599</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K81" s="6">
+        <v>9.85294248224589</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M81" s="4">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>11.7199896455827</v>
       </c>
@@ -3579,8 +3793,25 @@
       <c r="H82">
         <v>43731.402731864298</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K82" s="5">
+        <v>10.181545204642701</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M82" s="2">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>11.7641824126081</v>
       </c>
@@ -3599,8 +3830,25 @@
       <c r="H83">
         <v>4215.8835830804201</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K83" s="6">
+        <v>10.563042202035501</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M83" s="4">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>11.833500458229601</v>
       </c>
@@ -3619,8 +3867,20 @@
       <c r="H84">
         <v>26913.199174430301</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K84" s="7"/>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>11.8390682119754</v>
       </c>
@@ -3639,28 +3899,60 @@
       <c r="H85">
         <v>43843.966568616997</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K85" s="7"/>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>11.926137269756101</v>
+        <v>12.7885953862819</v>
       </c>
       <c r="B86" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="C86">
-        <v>89.766109735058905</v>
+        <v>97.013290493730096</v>
       </c>
       <c r="D86" t="b">
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="H86">
-        <v>115122.754473693</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>395358.45861314097</v>
+      </c>
+      <c r="I86">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>2.3525206725984002E-2</v>
+      </c>
+      <c r="K86" s="5">
+        <v>15.013722878434899</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M86" s="1">
+        <v>3.9846198979181748</v>
+      </c>
+      <c r="N86" s="2">
+        <v>3.9846198979181749E-2</v>
+      </c>
+      <c r="O86">
+        <f t="shared" si="1"/>
+        <v>3.9846198979181748</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>11.9346012791465</v>
       </c>
@@ -3679,28 +3971,60 @@
       <c r="H87">
         <v>20907.264062485701</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K87" s="7"/>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>12.084716107508299</v>
+        <v>10.9970390679324</v>
       </c>
       <c r="B88" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C88">
-        <v>94.960123063347496</v>
+        <v>89.423779677660306</v>
       </c>
       <c r="D88" t="b">
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H88">
-        <v>418485.651543974</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>394381.45044526801</v>
+      </c>
+      <c r="I88">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>2.3467071333604105E-2</v>
+      </c>
+      <c r="K88" s="6">
+        <v>9.5564512669485797</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M88" s="3">
+        <v>3.760397893499968</v>
+      </c>
+      <c r="N88" s="4">
+        <v>3.7603978934999678E-2</v>
+      </c>
+      <c r="O88">
+        <f t="shared" si="1"/>
+        <v>3.760397893499968</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>12.1073475677548</v>
       </c>
@@ -3719,8 +4043,20 @@
       <c r="H89">
         <v>23017.806720568798</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K89" s="7"/>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>12.1475882756377</v>
       </c>
@@ -3739,8 +4075,20 @@
       <c r="H90">
         <v>37299.331123252203</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K90" s="7"/>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>12.154638755431099</v>
       </c>
@@ -3759,8 +4107,20 @@
       <c r="H91">
         <v>48193.385892635903</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K91" s="7"/>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>12.159274852275001</v>
       </c>
@@ -3779,48 +4139,100 @@
       <c r="H92">
         <v>48193.385892635903</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K92" s="7"/>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>12.387462201877501</v>
+        <v>10.7284068068968</v>
       </c>
       <c r="B93" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C93">
-        <v>93.864025219451804</v>
+        <v>98.229805038712101</v>
       </c>
       <c r="D93" t="b">
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H93">
-        <v>220786.109694949</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+        <v>383968.05209737399</v>
+      </c>
+      <c r="I93">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>2.2847437825031729E-2</v>
+      </c>
+      <c r="K93" s="5">
+        <v>12.728796606709</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M93" s="1">
+        <v>3.2799038189606713</v>
+      </c>
+      <c r="N93" s="2">
+        <v>3.2799038189606715E-2</v>
+      </c>
+      <c r="O93">
+        <f t="shared" si="1"/>
+        <v>3.2799038189606713</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>12.472356621966499</v>
+        <v>11.465407386451799</v>
       </c>
       <c r="B94" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C94">
-        <v>93.873666384500396</v>
+        <v>90.207956351643304</v>
       </c>
       <c r="D94" t="b">
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H94">
-        <v>142073.440774324</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>355383.19510815298</v>
+      </c>
+      <c r="I94">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>2.114653917153379E-2</v>
+      </c>
+      <c r="K94" s="6">
+        <v>14.082482111214899</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M94" s="3">
+        <v>2.9869958228649471</v>
+      </c>
+      <c r="N94" s="4">
+        <v>2.9869958228649469E-2</v>
+      </c>
+      <c r="O94">
+        <f t="shared" si="1"/>
+        <v>2.9869958228649471</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>12.4830241598954</v>
       </c>
@@ -3839,8 +4251,20 @@
       <c r="H95">
         <v>14469.4102987305</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K95" s="7"/>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>12.518138800139599</v>
       </c>
@@ -3859,8 +4283,20 @@
       <c r="H96">
         <v>36341.245194302399</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K96" s="7"/>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>12.5805285874885</v>
       </c>
@@ -3879,8 +4315,20 @@
       <c r="H97">
         <v>20674.537259642901</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K97" s="7"/>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>12.7024210276931</v>
       </c>
@@ -3899,36 +4347,68 @@
       <c r="H98">
         <v>3639.1609586670502</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K98" s="7"/>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>12.728796606709</v>
+        <v>16.353955469231298</v>
       </c>
       <c r="B99" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C99">
-        <v>95.808001683239695</v>
+        <v>94.918703250514994</v>
       </c>
       <c r="D99" t="b">
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H99">
-        <v>551212.03965080401</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+        <v>302072.55660798098</v>
+      </c>
+      <c r="I99">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>1.7974370310368911E-2</v>
+      </c>
+      <c r="K99" s="5">
+        <v>12.084716107508299</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M99" s="1">
+        <v>2.4901355339568965</v>
+      </c>
+      <c r="N99" s="2">
+        <v>2.4901355339568967E-2</v>
+      </c>
+      <c r="O99">
+        <f t="shared" si="1"/>
+        <v>2.4901355339568965</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>12.7885953862819</v>
+        <v>12.387462201877501</v>
       </c>
       <c r="B100" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C100">
-        <v>97.013290493730096</v>
+        <v>93.864025219451804</v>
       </c>
       <c r="D100" t="b">
         <v>1</v>
@@ -3937,10 +4417,30 @@
         <v>26</v>
       </c>
       <c r="H100">
-        <v>395358.45861314097</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>220786.109694949</v>
+      </c>
+      <c r="I100">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>1.3137543309480153E-2</v>
+      </c>
+      <c r="K100" s="6">
+        <v>9.85294248224589</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M100" s="3">
+        <v>2.4544954858796322</v>
+      </c>
+      <c r="N100" s="4">
+        <v>2.454495485879632E-2</v>
+      </c>
+      <c r="O100">
+        <f t="shared" si="1"/>
+        <v>2.4544954858796322</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>12.914730904326801</v>
       </c>
@@ -3959,8 +4459,20 @@
       <c r="H101">
         <v>90562.5295076443</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K101" s="7"/>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>13.0179949608115</v>
       </c>
@@ -3979,8 +4491,20 @@
       <c r="H102">
         <v>47089.4194560084</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K102" s="7"/>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>13.0849246818774</v>
       </c>
@@ -3999,8 +4523,20 @@
       <c r="H103">
         <v>14392.5772729491</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K103" s="7"/>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>13.1366237349781</v>
       </c>
@@ -4019,8 +4555,20 @@
       <c r="H104">
         <v>99819.883926172697</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K104" s="7"/>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>13.2104666712357</v>
       </c>
@@ -4039,8 +4587,20 @@
       <c r="H105">
         <v>28103.986553491701</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K105" s="7"/>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>13.2655442209265</v>
       </c>
@@ -4059,8 +4619,20 @@
       <c r="H106">
         <v>30169.467286589901</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K106" s="7"/>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>13.3019826320467</v>
       </c>
@@ -4079,8 +4651,20 @@
       <c r="H107">
         <v>20238.182803375901</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K107" s="7"/>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>13.3324538657485</v>
       </c>
@@ -4099,8 +4683,20 @@
       <c r="H108">
         <v>15660.4061242755</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K108" s="7"/>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>13.3514733460666</v>
       </c>
@@ -4119,8 +4715,20 @@
       <c r="H109">
         <v>99980.645467378796</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K109" s="7"/>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>13.4724678053161</v>
       </c>
@@ -4139,8 +4747,20 @@
       <c r="H110">
         <v>8694.6170693972399</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K110" s="7"/>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>13.523348106516201</v>
       </c>
@@ -4159,8 +4779,20 @@
       <c r="H111">
         <v>96893.6237674898</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K111" s="7"/>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>13.596801003430601</v>
       </c>
@@ -4179,8 +4811,20 @@
       <c r="H112">
         <v>10606.7626845594</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K112" s="7"/>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>13.641833802631901</v>
       </c>
@@ -4199,28 +4843,60 @@
       <c r="H113">
         <v>18376.837698749299</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K113" s="7"/>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>13.720375473353201</v>
+        <v>15.972004765723501</v>
       </c>
       <c r="B114" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C114">
-        <v>96.322585730815803</v>
+        <v>85.0428570686272</v>
       </c>
       <c r="D114" t="b">
         <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H114">
-        <v>605178.32783679396</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>217022.545470301</v>
+      </c>
+      <c r="I114">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>1.2913598116244773E-2</v>
+      </c>
+      <c r="K114" s="5">
+        <v>12.7885953862819</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M114" s="1">
+        <v>2.3525206725984003</v>
+      </c>
+      <c r="N114" s="2">
+        <v>2.3525206725984002E-2</v>
+      </c>
+      <c r="O114">
+        <f t="shared" si="1"/>
+        <v>2.3525206725984003</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>13.858064869938801</v>
       </c>
@@ -4239,8 +4915,20 @@
       <c r="H115">
         <v>64876.118765686202</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K115" s="7"/>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>13.9018707302914</v>
       </c>
@@ -4259,8 +4947,20 @@
       <c r="H116">
         <v>22968.2129977146</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K116" s="7"/>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>13.9499943821789</v>
       </c>
@@ -4279,8 +4979,20 @@
       <c r="H117">
         <v>117475.830010787</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K117" s="7"/>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>13.9723662292801</v>
       </c>
@@ -4299,8 +5011,20 @@
       <c r="H118">
         <v>10899.2449939985</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K118" s="7"/>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>13.972604279494499</v>
       </c>
@@ -4319,8 +5043,20 @@
       <c r="H119">
         <v>10899.2449939985</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K119" s="7"/>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>14.0520140341381</v>
       </c>
@@ -4339,8 +5075,20 @@
       <c r="H120">
         <v>17587.082529815201</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K120" s="7"/>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>14.0570257999277</v>
       </c>
@@ -4359,28 +5107,60 @@
       <c r="H121">
         <v>163259.80421147199</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K121" s="7"/>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>14.082482111214899</v>
+        <v>10.563042202035501</v>
       </c>
       <c r="B122" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C122">
-        <v>88.051553401317094</v>
+        <v>97.589159336245203</v>
       </c>
       <c r="D122" t="b">
         <v>1</v>
       </c>
       <c r="E122" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H122">
-        <v>501986.68949736102</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>187550.071788587</v>
+      </c>
+      <c r="I122">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>1.1159883174820223E-2</v>
+      </c>
+      <c r="K122" s="6">
+        <v>10.9970390679324</v>
+      </c>
+      <c r="L122" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M122" s="3">
+        <v>2.3467071333604106</v>
+      </c>
+      <c r="N122" s="4">
+        <v>2.3467071333604105E-2</v>
+      </c>
+      <c r="O122">
+        <f t="shared" si="1"/>
+        <v>2.3467071333604106</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>14.1666048515771</v>
       </c>
@@ -4399,8 +5179,12 @@
       <c r="H123">
         <v>11871.782200788601</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N123">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>14.2468383073194</v>
       </c>
@@ -4419,8 +5203,12 @@
       <c r="H124">
         <v>20034.579979451399</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>14.337633153981299</v>
       </c>
@@ -4439,8 +5227,12 @@
       <c r="H125">
         <v>11894.2926352226</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N125">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>14.3884456091094</v>
       </c>
@@ -4459,8 +5251,12 @@
       <c r="H126">
         <v>60044.4213425747</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>14.3889001651721</v>
       </c>
@@ -4479,8 +5275,12 @@
       <c r="H127">
         <v>60044.4213425747</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N127">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>14.4319743358634</v>
       </c>
@@ -4499,8 +5299,12 @@
       <c r="H128">
         <v>17858.165111877301</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N128">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>14.495817535788399</v>
       </c>
@@ -4519,8 +5323,12 @@
       <c r="H129">
         <v>44920.636882905601</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>14.5162813031759</v>
       </c>
@@ -4539,8 +5347,12 @@
       <c r="H130">
         <v>15057.653945296001</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N130">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>14.5505513065311</v>
       </c>
@@ -4559,8 +5371,12 @@
       <c r="H131">
         <v>76074.012580140305</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N131">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>14.603923618328</v>
       </c>
@@ -4579,8 +5395,12 @@
       <c r="H132">
         <v>17171.662436779199</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N132">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>14.700903952670499</v>
       </c>
@@ -4599,8 +5419,12 @@
       <c r="H133">
         <v>23729.601515942501</v>
       </c>
-    </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N133">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>14.827630486071699</v>
       </c>
@@ -4619,8 +5443,12 @@
       <c r="H134">
         <v>14900.806515865201</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N134">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>14.9037206558523</v>
       </c>
@@ -4639,8 +5467,12 @@
       <c r="H135">
         <v>138093.51284795001</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N135">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>14.9754176217679</v>
       </c>
@@ -4659,28 +5491,36 @@
       <c r="H136">
         <v>300135.233133192</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="N136">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>15.013722878434899</v>
+        <v>16.063060793866899</v>
       </c>
       <c r="B137" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C137">
-        <v>91.142814938348494</v>
+        <v>86.677885808107007</v>
       </c>
       <c r="D137" t="b">
         <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H137">
-        <v>669644.77691929298</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>154111.29887535999</v>
+      </c>
+      <c r="I137">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>9.1701596004053337E-3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>15.023316619352199</v>
       </c>
@@ -4700,7 +5540,7 @@
         <v>96484.136351083303</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>15.0331980344321</v>
       </c>
@@ -4720,7 +5560,7 @@
         <v>170728.07827035</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>15.055553004168001</v>
       </c>
@@ -4740,7 +5580,7 @@
         <v>12007.948117056399</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>15.275822506154</v>
       </c>
@@ -4760,7 +5600,7 @@
         <v>101187.506676693</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>15.3634436799921</v>
       </c>
@@ -4780,7 +5620,7 @@
         <v>7231.4634897504802</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>15.4489711803147</v>
       </c>
@@ -4800,7 +5640,7 @@
         <v>3413.4542240494802</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>15.4950021621631</v>
       </c>
@@ -4820,7 +5660,7 @@
         <v>8340.5641601559491</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>15.5149873086313</v>
       </c>
@@ -4840,7 +5680,7 @@
         <v>68766.030900024096</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>15.7580494541328</v>
       </c>
@@ -4860,7 +5700,7 @@
         <v>9085.3678463820597</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>15.854133476513899</v>
       </c>
@@ -4880,7 +5720,7 @@
         <v>22890.150485006001</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>15.868609003038699</v>
       </c>
@@ -4900,7 +5740,7 @@
         <v>90232.208630877096</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>15.878453999887</v>
       </c>
@@ -4920,7 +5760,7 @@
         <v>19785.735425794701</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>15.894453869287201</v>
       </c>
@@ -4940,7 +5780,7 @@
         <v>34293.063933993697</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>15.9661127816329</v>
       </c>
@@ -4960,27 +5800,31 @@
         <v>78311.543039553304</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>15.972004765723501</v>
+        <v>12.472356621966499</v>
       </c>
       <c r="B152" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C152">
-        <v>85.0428570686272</v>
+        <v>93.873666384500396</v>
       </c>
       <c r="D152" t="b">
         <v>1</v>
       </c>
       <c r="E152" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H152">
-        <v>217022.545470301</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>142073.440774324</v>
+      </c>
+      <c r="I152">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>8.4538650727548261E-3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>16.008032273605</v>
       </c>
@@ -5000,27 +5844,31 @@
         <v>4382.9535390660903</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>16.063060793866899</v>
+        <v>18.0140340784221</v>
       </c>
       <c r="B154" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C154">
-        <v>86.677885808107007</v>
+        <v>88.848454990420706</v>
       </c>
       <c r="D154" t="b">
         <v>1</v>
       </c>
       <c r="E154" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H154">
-        <v>154111.29887535999</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>120310.65743459899</v>
+      </c>
+      <c r="I154">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>7.1589035869281149E-3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>16.1080021087195</v>
       </c>
@@ -5040,7 +5888,7 @@
         <v>14591.932970681401</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>16.1242987985467</v>
       </c>
@@ -5060,7 +5908,7 @@
         <v>13335.6504350133</v>
       </c>
     </row>
-    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>16.141199438623801</v>
       </c>
@@ -5080,7 +5928,7 @@
         <v>28723.119222507899</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>16.2359528209081</v>
       </c>
@@ -5100,27 +5948,31 @@
         <v>4910.7754257483602</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>16.353955469231298</v>
+        <v>11.926137269756101</v>
       </c>
       <c r="B159" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C159">
-        <v>94.918703250514994</v>
+        <v>89.766109735058905</v>
       </c>
       <c r="D159" t="b">
         <v>1</v>
       </c>
       <c r="E159" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="H159">
-        <v>302072.55660798098</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>115122.754473693</v>
+      </c>
+      <c r="I159">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>6.8502052728518737E-3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>16.683752535158199</v>
       </c>
@@ -5140,7 +5992,7 @@
         <v>38210.3593421279</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>16.971534752194898</v>
       </c>
@@ -5160,7 +6012,7 @@
         <v>103292.48215387001</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>17.0460603414075</v>
       </c>
@@ -5180,7 +6032,7 @@
         <v>21834.2032741107</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>17.119869910738501</v>
       </c>
@@ -5200,7 +6052,7 @@
         <v>30457.432673862699</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>17.217928040709001</v>
       </c>
@@ -5220,7 +6072,7 @@
         <v>20459.410012548698</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>17.3162541126948</v>
       </c>
@@ -5240,7 +6092,7 @@
         <v>4368.6792897749601</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>17.379330463588399</v>
       </c>
@@ -5260,7 +6112,7 @@
         <v>32943.578547569603</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>17.460976987465401</v>
       </c>
@@ -5280,7 +6132,7 @@
         <v>36668.180313255201</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>17.509958413433601</v>
       </c>
@@ -5300,7 +6152,7 @@
         <v>18789.2614993641</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>17.572997416703501</v>
       </c>
@@ -5320,7 +6172,7 @@
         <v>25231.3539607046</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>17.646850969481601</v>
       </c>
@@ -5340,27 +6192,31 @@
         <v>12313.302517874999</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>18.0140340784221</v>
+        <v>10.181545204642701</v>
       </c>
       <c r="B171" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C171">
-        <v>88.848454990420706</v>
+        <v>94.500177342310394</v>
       </c>
       <c r="D171" t="b">
         <v>1</v>
       </c>
       <c r="E171" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H171">
-        <v>120310.65743459899</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>105211.401042495</v>
+      </c>
+      <c r="I171">
+        <f>Table1[[#This Row],[Base Peak Area]]/$K$22</f>
+        <v>6.2604451872294792E-3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>18.187472053170001</v>
       </c>
@@ -5380,7 +6236,7 @@
         <v>33774.877500791401</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>18.389159236756001</v>
       </c>
@@ -5400,7 +6256,7 @@
         <v>16949.220953733598</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>18.557818392862998</v>
       </c>
@@ -5420,7 +6276,7 @@
         <v>48825.957611390302</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>18.703178277947298</v>
       </c>
@@ -5440,7 +6296,7 @@
         <v>10948.6754408046</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>18.790684130648501</v>
       </c>
